--- a/output/version3/test/15-5/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-5/MARL/IL/RL-RL (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>702</v>
+        <v>735</v>
       </c>
       <c r="C2" t="n">
-        <v>670</v>
+        <v>647</v>
       </c>
       <c r="D2" t="n">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="E2" t="n">
-        <v>698</v>
+        <v>727</v>
       </c>
       <c r="F2" t="n">
-        <v>588</v>
+        <v>656</v>
       </c>
       <c r="G2" t="n">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="H2" t="n">
-        <v>594</v>
+        <v>676</v>
       </c>
       <c r="I2" t="n">
-        <v>680</v>
+        <v>657</v>
       </c>
       <c r="J2" t="n">
-        <v>642</v>
+        <v>532</v>
       </c>
       <c r="K2" t="n">
-        <v>610</v>
+        <v>752</v>
       </c>
       <c r="L2" t="n">
-        <v>640.1</v>
+        <v>660.3</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>741</v>
+        <v>706</v>
       </c>
       <c r="C3" t="n">
-        <v>757</v>
+        <v>717</v>
       </c>
       <c r="D3" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="E3" t="n">
-        <v>732</v>
+        <v>745</v>
       </c>
       <c r="F3" t="n">
-        <v>740</v>
+        <v>642</v>
       </c>
       <c r="G3" t="n">
-        <v>752</v>
+        <v>684</v>
       </c>
       <c r="H3" t="n">
-        <v>745</v>
+        <v>850</v>
       </c>
       <c r="I3" t="n">
-        <v>748</v>
+        <v>764</v>
       </c>
       <c r="J3" t="n">
-        <v>756</v>
+        <v>676</v>
       </c>
       <c r="K3" t="n">
-        <v>865</v>
+        <v>642</v>
       </c>
       <c r="L3" t="n">
-        <v>759.1</v>
+        <v>721.4</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>753</v>
+        <v>809</v>
       </c>
       <c r="C4" t="n">
-        <v>737</v>
+        <v>773</v>
       </c>
       <c r="D4" t="n">
-        <v>828</v>
+        <v>849</v>
       </c>
       <c r="E4" t="n">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="F4" t="n">
-        <v>792</v>
+        <v>862</v>
       </c>
       <c r="G4" t="n">
-        <v>792</v>
+        <v>719</v>
       </c>
       <c r="H4" t="n">
+        <v>724</v>
+      </c>
+      <c r="I4" t="n">
+        <v>743</v>
+      </c>
+      <c r="J4" t="n">
+        <v>705</v>
+      </c>
+      <c r="K4" t="n">
         <v>793</v>
       </c>
-      <c r="I4" t="n">
-        <v>775</v>
-      </c>
-      <c r="J4" t="n">
-        <v>780</v>
-      </c>
-      <c r="K4" t="n">
-        <v>710</v>
-      </c>
       <c r="L4" t="n">
-        <v>773.2</v>
+        <v>773.3</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>836</v>
+        <v>874</v>
       </c>
       <c r="C5" t="n">
-        <v>909</v>
+        <v>788</v>
       </c>
       <c r="D5" t="n">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="E5" t="n">
+        <v>805</v>
+      </c>
+      <c r="F5" t="n">
+        <v>806</v>
+      </c>
+      <c r="G5" t="n">
         <v>937</v>
       </c>
-      <c r="F5" t="n">
-        <v>903</v>
-      </c>
-      <c r="G5" t="n">
-        <v>930</v>
-      </c>
       <c r="H5" t="n">
-        <v>944</v>
+        <v>919</v>
       </c>
       <c r="I5" t="n">
-        <v>876</v>
+        <v>826</v>
       </c>
       <c r="J5" t="n">
-        <v>905</v>
+        <v>942</v>
       </c>
       <c r="K5" t="n">
-        <v>836</v>
+        <v>885</v>
       </c>
       <c r="L5" t="n">
-        <v>890.6</v>
+        <v>862.4</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>746</v>
+        <v>675</v>
       </c>
       <c r="C6" t="n">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="D6" t="n">
-        <v>649</v>
+        <v>618</v>
       </c>
       <c r="E6" t="n">
-        <v>711</v>
+        <v>738</v>
       </c>
       <c r="F6" t="n">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="G6" t="n">
-        <v>603</v>
+        <v>677</v>
       </c>
       <c r="H6" t="n">
-        <v>680</v>
+        <v>652</v>
       </c>
       <c r="I6" t="n">
         <v>642</v>
       </c>
       <c r="J6" t="n">
-        <v>596</v>
+        <v>644</v>
       </c>
       <c r="K6" t="n">
-        <v>638</v>
+        <v>743</v>
       </c>
       <c r="L6" t="n">
-        <v>657.2</v>
+        <v>666.9</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>832</v>
+        <v>796</v>
       </c>
       <c r="C7" t="n">
+        <v>827</v>
+      </c>
+      <c r="D7" t="n">
+        <v>867</v>
+      </c>
+      <c r="E7" t="n">
+        <v>831</v>
+      </c>
+      <c r="F7" t="n">
+        <v>804</v>
+      </c>
+      <c r="G7" t="n">
         <v>788</v>
       </c>
-      <c r="D7" t="n">
-        <v>793</v>
-      </c>
-      <c r="E7" t="n">
-        <v>792</v>
-      </c>
-      <c r="F7" t="n">
-        <v>866</v>
-      </c>
-      <c r="G7" t="n">
-        <v>834</v>
-      </c>
       <c r="H7" t="n">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I7" t="n">
-        <v>762</v>
+        <v>827</v>
       </c>
       <c r="J7" t="n">
-        <v>867</v>
+        <v>856</v>
       </c>
       <c r="K7" t="n">
-        <v>858</v>
+        <v>780</v>
       </c>
       <c r="L7" t="n">
-        <v>820.8</v>
+        <v>819.1</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>727</v>
+        <v>663</v>
       </c>
       <c r="C8" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="D8" t="n">
-        <v>728</v>
+        <v>818</v>
       </c>
       <c r="E8" t="n">
-        <v>652</v>
+        <v>825</v>
       </c>
       <c r="F8" t="n">
-        <v>688</v>
+        <v>714</v>
       </c>
       <c r="G8" t="n">
-        <v>700</v>
+        <v>666</v>
       </c>
       <c r="H8" t="n">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="I8" t="n">
-        <v>711</v>
+        <v>767</v>
       </c>
       <c r="J8" t="n">
-        <v>677</v>
+        <v>778</v>
       </c>
       <c r="K8" t="n">
-        <v>672</v>
+        <v>760</v>
       </c>
       <c r="L8" t="n">
-        <v>683.2</v>
+        <v>729.8</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>667</v>
+        <v>695</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="D9" t="n">
-        <v>718</v>
+        <v>687</v>
       </c>
       <c r="E9" t="n">
-        <v>640</v>
+        <v>721</v>
       </c>
       <c r="F9" t="n">
-        <v>643</v>
+        <v>588</v>
       </c>
       <c r="G9" t="n">
-        <v>734</v>
+        <v>677</v>
       </c>
       <c r="H9" t="n">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="I9" t="n">
-        <v>609</v>
+        <v>676</v>
       </c>
       <c r="J9" t="n">
-        <v>635</v>
+        <v>611</v>
       </c>
       <c r="K9" t="n">
-        <v>699</v>
+        <v>660</v>
       </c>
       <c r="L9" t="n">
-        <v>663.1</v>
+        <v>661</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>764</v>
+        <v>791</v>
       </c>
       <c r="C10" t="n">
-        <v>749</v>
+        <v>919</v>
       </c>
       <c r="D10" t="n">
-        <v>835</v>
+        <v>794</v>
       </c>
       <c r="E10" t="n">
-        <v>790</v>
+        <v>860</v>
       </c>
       <c r="F10" t="n">
-        <v>818</v>
+        <v>956</v>
       </c>
       <c r="G10" t="n">
+        <v>783</v>
+      </c>
+      <c r="H10" t="n">
+        <v>789</v>
+      </c>
+      <c r="I10" t="n">
+        <v>900</v>
+      </c>
+      <c r="J10" t="n">
+        <v>967</v>
+      </c>
+      <c r="K10" t="n">
         <v>810</v>
       </c>
-      <c r="H10" t="n">
-        <v>773</v>
-      </c>
-      <c r="I10" t="n">
-        <v>868</v>
-      </c>
-      <c r="J10" t="n">
-        <v>816</v>
-      </c>
-      <c r="K10" t="n">
-        <v>800</v>
-      </c>
       <c r="L10" t="n">
-        <v>802.3</v>
+        <v>856.9</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>810</v>
+        <v>766</v>
       </c>
       <c r="C11" t="n">
-        <v>881</v>
+        <v>725</v>
       </c>
       <c r="D11" t="n">
-        <v>746</v>
+        <v>844</v>
       </c>
       <c r="E11" t="n">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="F11" t="n">
-        <v>782</v>
+        <v>813</v>
       </c>
       <c r="G11" t="n">
-        <v>787</v>
+        <v>812</v>
       </c>
       <c r="H11" t="n">
-        <v>790</v>
+        <v>715</v>
       </c>
       <c r="I11" t="n">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="J11" t="n">
-        <v>767</v>
+        <v>806</v>
       </c>
       <c r="K11" t="n">
-        <v>795</v>
+        <v>744</v>
       </c>
       <c r="L11" t="n">
-        <v>792.9</v>
+        <v>783.8</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="C12" t="n">
-        <v>707</v>
+        <v>739</v>
       </c>
       <c r="D12" t="n">
-        <v>660</v>
+        <v>706</v>
       </c>
       <c r="E12" t="n">
-        <v>701</v>
+        <v>627</v>
       </c>
       <c r="F12" t="n">
-        <v>712</v>
+        <v>735</v>
       </c>
       <c r="G12" t="n">
-        <v>758</v>
+        <v>680</v>
       </c>
       <c r="H12" t="n">
-        <v>687</v>
+        <v>821</v>
       </c>
       <c r="I12" t="n">
-        <v>750</v>
+        <v>633</v>
       </c>
       <c r="J12" t="n">
-        <v>627</v>
+        <v>682</v>
       </c>
       <c r="K12" t="n">
-        <v>761</v>
+        <v>664</v>
       </c>
       <c r="L12" t="n">
-        <v>708.4</v>
+        <v>702.4</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C13" t="n">
-        <v>584</v>
+        <v>625</v>
       </c>
       <c r="D13" t="n">
-        <v>636</v>
+        <v>767</v>
       </c>
       <c r="E13" t="n">
-        <v>635</v>
+        <v>592</v>
       </c>
       <c r="F13" t="n">
-        <v>555</v>
+        <v>506</v>
       </c>
       <c r="G13" t="n">
-        <v>619</v>
+        <v>750</v>
       </c>
       <c r="H13" t="n">
-        <v>601</v>
+        <v>549</v>
       </c>
       <c r="I13" t="n">
-        <v>558</v>
+        <v>685</v>
       </c>
       <c r="J13" t="n">
-        <v>727</v>
+        <v>660</v>
       </c>
       <c r="K13" t="n">
-        <v>553</v>
+        <v>667</v>
       </c>
       <c r="L13" t="n">
-        <v>613.9</v>
+        <v>647.3</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>718</v>
+        <v>622</v>
       </c>
       <c r="C14" t="n">
-        <v>761</v>
+        <v>641</v>
       </c>
       <c r="D14" t="n">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="E14" t="n">
         <v>702</v>
       </c>
       <c r="F14" t="n">
-        <v>618</v>
+        <v>684</v>
       </c>
       <c r="G14" t="n">
+        <v>712</v>
+      </c>
+      <c r="H14" t="n">
+        <v>683</v>
+      </c>
+      <c r="I14" t="n">
+        <v>607</v>
+      </c>
+      <c r="J14" t="n">
+        <v>736</v>
+      </c>
+      <c r="K14" t="n">
         <v>593</v>
       </c>
-      <c r="H14" t="n">
-        <v>634</v>
-      </c>
-      <c r="I14" t="n">
-        <v>701</v>
-      </c>
-      <c r="J14" t="n">
-        <v>662</v>
-      </c>
-      <c r="K14" t="n">
-        <v>675</v>
-      </c>
       <c r="L14" t="n">
-        <v>679</v>
+        <v>673.3</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>666</v>
+        <v>699</v>
       </c>
       <c r="C15" t="n">
-        <v>702</v>
+        <v>678</v>
       </c>
       <c r="D15" t="n">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="E15" t="n">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="F15" t="n">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="G15" t="n">
-        <v>745</v>
+        <v>714</v>
       </c>
       <c r="H15" t="n">
-        <v>637</v>
+        <v>718</v>
       </c>
       <c r="I15" t="n">
-        <v>664</v>
+        <v>715</v>
       </c>
       <c r="J15" t="n">
-        <v>688</v>
+        <v>665</v>
       </c>
       <c r="K15" t="n">
-        <v>725</v>
+        <v>772</v>
       </c>
       <c r="L15" t="n">
-        <v>701</v>
+        <v>718.2</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>734</v>
+        <v>747</v>
       </c>
       <c r="C16" t="n">
-        <v>710</v>
+        <v>723</v>
       </c>
       <c r="D16" t="n">
-        <v>759</v>
+        <v>730</v>
       </c>
       <c r="E16" t="n">
-        <v>791</v>
+        <v>724</v>
       </c>
       <c r="F16" t="n">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="G16" t="n">
-        <v>643</v>
+        <v>808</v>
       </c>
       <c r="H16" t="n">
-        <v>708</v>
+        <v>745</v>
       </c>
       <c r="I16" t="n">
-        <v>672</v>
+        <v>700</v>
       </c>
       <c r="J16" t="n">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="K16" t="n">
-        <v>671</v>
+        <v>781</v>
       </c>
       <c r="L16" t="n">
-        <v>718.2</v>
+        <v>744</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>916</v>
+        <v>830</v>
       </c>
       <c r="C17" t="n">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="D17" t="n">
-        <v>826</v>
+        <v>839</v>
       </c>
       <c r="E17" t="n">
-        <v>804</v>
+        <v>750</v>
       </c>
       <c r="F17" t="n">
-        <v>766</v>
+        <v>873</v>
       </c>
       <c r="G17" t="n">
-        <v>845</v>
+        <v>801</v>
       </c>
       <c r="H17" t="n">
-        <v>798</v>
+        <v>842</v>
       </c>
       <c r="I17" t="n">
-        <v>715</v>
+        <v>762</v>
       </c>
       <c r="J17" t="n">
-        <v>893</v>
+        <v>760</v>
       </c>
       <c r="K17" t="n">
-        <v>873</v>
+        <v>853</v>
       </c>
       <c r="L17" t="n">
-        <v>833.7</v>
+        <v>821.7</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>657</v>
+        <v>714</v>
       </c>
       <c r="C18" t="n">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="D18" t="n">
-        <v>725</v>
+        <v>656</v>
       </c>
       <c r="E18" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="F18" t="n">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="G18" t="n">
-        <v>665</v>
+        <v>691</v>
       </c>
       <c r="H18" t="n">
-        <v>660</v>
+        <v>707</v>
       </c>
       <c r="I18" t="n">
-        <v>692</v>
+        <v>737</v>
       </c>
       <c r="J18" t="n">
-        <v>682</v>
+        <v>646</v>
       </c>
       <c r="K18" t="n">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="L18" t="n">
-        <v>669.8</v>
+        <v>677.1</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>657</v>
+        <v>741</v>
       </c>
       <c r="C19" t="n">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="D19" t="n">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="E19" t="n">
-        <v>785</v>
+        <v>660</v>
       </c>
       <c r="F19" t="n">
-        <v>692</v>
+        <v>713</v>
       </c>
       <c r="G19" t="n">
-        <v>768</v>
+        <v>649</v>
       </c>
       <c r="H19" t="n">
-        <v>714</v>
+        <v>727</v>
       </c>
       <c r="I19" t="n">
-        <v>761</v>
+        <v>660</v>
       </c>
       <c r="J19" t="n">
-        <v>795</v>
+        <v>666</v>
       </c>
       <c r="K19" t="n">
-        <v>752</v>
+        <v>706</v>
       </c>
       <c r="L19" t="n">
-        <v>740.6</v>
+        <v>698.7</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="C20" t="n">
-        <v>656</v>
+        <v>615</v>
       </c>
       <c r="D20" t="n">
-        <v>652</v>
+        <v>690</v>
       </c>
       <c r="E20" t="n">
-        <v>663</v>
+        <v>753</v>
       </c>
       <c r="F20" t="n">
-        <v>729</v>
+        <v>814</v>
       </c>
       <c r="G20" t="n">
-        <v>801</v>
+        <v>677</v>
       </c>
       <c r="H20" t="n">
-        <v>712</v>
+        <v>797</v>
       </c>
       <c r="I20" t="n">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="J20" t="n">
-        <v>705</v>
+        <v>769</v>
       </c>
       <c r="K20" t="n">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="L20" t="n">
-        <v>694.9</v>
+        <v>717.1</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>725</v>
+        <v>657</v>
       </c>
       <c r="C21" t="n">
-        <v>705</v>
+        <v>682</v>
       </c>
       <c r="D21" t="n">
-        <v>724</v>
+        <v>666</v>
       </c>
       <c r="E21" t="n">
-        <v>793</v>
+        <v>688</v>
       </c>
       <c r="F21" t="n">
-        <v>579</v>
+        <v>610</v>
       </c>
       <c r="G21" t="n">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="H21" t="n">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="I21" t="n">
-        <v>692</v>
+        <v>599</v>
       </c>
       <c r="J21" t="n">
-        <v>728</v>
+        <v>662</v>
       </c>
       <c r="K21" t="n">
-        <v>783</v>
+        <v>716</v>
       </c>
       <c r="L21" t="n">
-        <v>710.2</v>
+        <v>666.1</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>666</v>
+        <v>561</v>
       </c>
       <c r="C22" t="n">
-        <v>566</v>
+        <v>631</v>
       </c>
       <c r="D22" t="n">
-        <v>675</v>
+        <v>592</v>
       </c>
       <c r="E22" t="n">
-        <v>726</v>
+        <v>552</v>
       </c>
       <c r="F22" t="n">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="G22" t="n">
-        <v>596</v>
+        <v>634</v>
       </c>
       <c r="H22" t="n">
-        <v>592</v>
+        <v>656</v>
       </c>
       <c r="I22" t="n">
-        <v>671</v>
+        <v>605</v>
       </c>
       <c r="J22" t="n">
-        <v>638</v>
+        <v>552</v>
       </c>
       <c r="K22" t="n">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="L22" t="n">
-        <v>639.9</v>
+        <v>606.8</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>724</v>
+        <v>814</v>
       </c>
       <c r="C23" t="n">
-        <v>650</v>
+        <v>770</v>
       </c>
       <c r="D23" t="n">
-        <v>843</v>
+        <v>825</v>
       </c>
       <c r="E23" t="n">
-        <v>930</v>
+        <v>734</v>
       </c>
       <c r="F23" t="n">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="G23" t="n">
-        <v>784</v>
+        <v>766</v>
       </c>
       <c r="H23" t="n">
-        <v>824</v>
+        <v>659</v>
       </c>
       <c r="I23" t="n">
-        <v>808</v>
+        <v>757</v>
       </c>
       <c r="J23" t="n">
-        <v>772</v>
+        <v>686</v>
       </c>
       <c r="K23" t="n">
-        <v>919</v>
+        <v>747</v>
       </c>
       <c r="L23" t="n">
-        <v>802.6</v>
+        <v>751.8</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>852</v>
+        <v>666</v>
       </c>
       <c r="C24" t="n">
-        <v>685</v>
+        <v>657</v>
       </c>
       <c r="D24" t="n">
-        <v>729</v>
+        <v>858</v>
       </c>
       <c r="E24" t="n">
-        <v>727</v>
+        <v>810</v>
       </c>
       <c r="F24" t="n">
-        <v>715</v>
+        <v>674</v>
       </c>
       <c r="G24" t="n">
-        <v>709</v>
+        <v>735</v>
       </c>
       <c r="H24" t="n">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="I24" t="n">
-        <v>758</v>
+        <v>821</v>
       </c>
       <c r="J24" t="n">
-        <v>727</v>
+        <v>686</v>
       </c>
       <c r="K24" t="n">
-        <v>684</v>
+        <v>743</v>
       </c>
       <c r="L24" t="n">
-        <v>736.8</v>
+        <v>742.5</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>616</v>
+        <v>703</v>
       </c>
       <c r="C25" t="n">
-        <v>707</v>
+        <v>644</v>
       </c>
       <c r="D25" t="n">
+        <v>633</v>
+      </c>
+      <c r="E25" t="n">
+        <v>669</v>
+      </c>
+      <c r="F25" t="n">
         <v>663</v>
       </c>
-      <c r="E25" t="n">
-        <v>681</v>
-      </c>
-      <c r="F25" t="n">
-        <v>667</v>
-      </c>
       <c r="G25" t="n">
-        <v>659</v>
+        <v>686</v>
       </c>
       <c r="H25" t="n">
-        <v>673</v>
+        <v>658</v>
       </c>
       <c r="I25" t="n">
-        <v>673</v>
+        <v>812</v>
       </c>
       <c r="J25" t="n">
-        <v>639</v>
+        <v>687</v>
       </c>
       <c r="K25" t="n">
-        <v>781</v>
+        <v>648</v>
       </c>
       <c r="L25" t="n">
-        <v>675.9</v>
+        <v>680.3</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="C26" t="n">
-        <v>831</v>
+        <v>763</v>
       </c>
       <c r="D26" t="n">
-        <v>825</v>
+        <v>780</v>
       </c>
       <c r="E26" t="n">
-        <v>770</v>
+        <v>706</v>
       </c>
       <c r="F26" t="n">
-        <v>846</v>
+        <v>774</v>
       </c>
       <c r="G26" t="n">
-        <v>725</v>
+        <v>769</v>
       </c>
       <c r="H26" t="n">
-        <v>722</v>
+        <v>760</v>
       </c>
       <c r="I26" t="n">
-        <v>832</v>
+        <v>760</v>
       </c>
       <c r="J26" t="n">
-        <v>771</v>
+        <v>812</v>
       </c>
       <c r="K26" t="n">
-        <v>725</v>
+        <v>795</v>
       </c>
       <c r="L26" t="n">
-        <v>784.7</v>
+        <v>766.9</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>752</v>
+        <v>770</v>
       </c>
       <c r="C27" t="n">
-        <v>803</v>
+        <v>814</v>
       </c>
       <c r="D27" t="n">
-        <v>774</v>
+        <v>804</v>
       </c>
       <c r="E27" t="n">
-        <v>757</v>
+        <v>771</v>
       </c>
       <c r="F27" t="n">
-        <v>725</v>
+        <v>834</v>
       </c>
       <c r="G27" t="n">
-        <v>832</v>
+        <v>727</v>
       </c>
       <c r="H27" t="n">
-        <v>807</v>
+        <v>843</v>
       </c>
       <c r="I27" t="n">
-        <v>801</v>
+        <v>827</v>
       </c>
       <c r="J27" t="n">
-        <v>804</v>
+        <v>772</v>
       </c>
       <c r="K27" t="n">
-        <v>785</v>
+        <v>821</v>
       </c>
       <c r="L27" t="n">
-        <v>784</v>
+        <v>798.3</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>716</v>
+        <v>669</v>
       </c>
       <c r="C28" t="n">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D28" t="n">
-        <v>630</v>
+        <v>649</v>
       </c>
       <c r="E28" t="n">
-        <v>653</v>
+        <v>712</v>
       </c>
       <c r="F28" t="n">
-        <v>663</v>
+        <v>717</v>
       </c>
       <c r="G28" t="n">
-        <v>642</v>
+        <v>664</v>
       </c>
       <c r="H28" t="n">
-        <v>751</v>
+        <v>675</v>
       </c>
       <c r="I28" t="n">
-        <v>650</v>
+        <v>694</v>
       </c>
       <c r="J28" t="n">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="K28" t="n">
-        <v>653</v>
+        <v>602</v>
       </c>
       <c r="L28" t="n">
-        <v>664</v>
+        <v>667.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>670</v>
+        <v>718</v>
       </c>
       <c r="C29" t="n">
-        <v>707</v>
+        <v>634</v>
       </c>
       <c r="D29" t="n">
-        <v>832</v>
+        <v>688</v>
       </c>
       <c r="E29" t="n">
-        <v>768</v>
+        <v>733</v>
       </c>
       <c r="F29" t="n">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="G29" t="n">
-        <v>632</v>
+        <v>791</v>
       </c>
       <c r="H29" t="n">
-        <v>741</v>
+        <v>794</v>
       </c>
       <c r="I29" t="n">
-        <v>729</v>
+        <v>654</v>
       </c>
       <c r="J29" t="n">
-        <v>679</v>
+        <v>706</v>
       </c>
       <c r="K29" t="n">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="L29" t="n">
-        <v>708.7</v>
+        <v>707.8</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>832</v>
+        <v>757</v>
       </c>
       <c r="C30" t="n">
-        <v>730</v>
+        <v>763</v>
       </c>
       <c r="D30" t="n">
-        <v>694</v>
+        <v>621</v>
       </c>
       <c r="E30" t="n">
-        <v>671</v>
+        <v>719</v>
       </c>
       <c r="F30" t="n">
-        <v>779</v>
+        <v>762</v>
       </c>
       <c r="G30" t="n">
-        <v>779</v>
+        <v>754</v>
       </c>
       <c r="H30" t="n">
-        <v>695</v>
+        <v>798</v>
       </c>
       <c r="I30" t="n">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="J30" t="n">
-        <v>823</v>
+        <v>757</v>
       </c>
       <c r="K30" t="n">
-        <v>903</v>
+        <v>767</v>
       </c>
       <c r="L30" t="n">
-        <v>768.4</v>
+        <v>747.8</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>702</v>
+        <v>716</v>
       </c>
       <c r="C31" t="n">
-        <v>674</v>
+        <v>688</v>
       </c>
       <c r="D31" t="n">
-        <v>713</v>
+        <v>640</v>
       </c>
       <c r="E31" t="n">
-        <v>811</v>
+        <v>767</v>
       </c>
       <c r="F31" t="n">
-        <v>731</v>
+        <v>682</v>
       </c>
       <c r="G31" t="n">
-        <v>750</v>
+        <v>662</v>
       </c>
       <c r="H31" t="n">
-        <v>699</v>
+        <v>742</v>
       </c>
       <c r="I31" t="n">
-        <v>792</v>
+        <v>654</v>
       </c>
       <c r="J31" t="n">
-        <v>724</v>
+        <v>737</v>
       </c>
       <c r="K31" t="n">
-        <v>758</v>
+        <v>803</v>
       </c>
       <c r="L31" t="n">
-        <v>735.4</v>
+        <v>709.1</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>665</v>
+        <v>776</v>
       </c>
       <c r="C32" t="n">
-        <v>617</v>
+        <v>669</v>
       </c>
       <c r="D32" t="n">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="E32" t="n">
-        <v>637</v>
+        <v>699</v>
       </c>
       <c r="F32" t="n">
-        <v>702</v>
+        <v>735</v>
       </c>
       <c r="G32" t="n">
-        <v>669</v>
+        <v>751</v>
       </c>
       <c r="H32" t="n">
-        <v>820</v>
+        <v>758</v>
       </c>
       <c r="I32" t="n">
-        <v>674</v>
+        <v>575</v>
       </c>
       <c r="J32" t="n">
-        <v>647</v>
+        <v>597</v>
       </c>
       <c r="K32" t="n">
-        <v>641</v>
+        <v>794</v>
       </c>
       <c r="L32" t="n">
-        <v>673</v>
+        <v>702.9</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>796</v>
+        <v>774</v>
       </c>
       <c r="C33" t="n">
-        <v>829</v>
+        <v>762</v>
       </c>
       <c r="D33" t="n">
-        <v>687</v>
+        <v>771</v>
       </c>
       <c r="E33" t="n">
-        <v>753</v>
+        <v>867</v>
       </c>
       <c r="F33" t="n">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="G33" t="n">
-        <v>787</v>
+        <v>721</v>
       </c>
       <c r="H33" t="n">
+        <v>877</v>
+      </c>
+      <c r="I33" t="n">
+        <v>729</v>
+      </c>
+      <c r="J33" t="n">
+        <v>719</v>
+      </c>
+      <c r="K33" t="n">
         <v>742</v>
       </c>
-      <c r="I33" t="n">
-        <v>791</v>
-      </c>
-      <c r="J33" t="n">
-        <v>723</v>
-      </c>
-      <c r="K33" t="n">
-        <v>781</v>
-      </c>
       <c r="L33" t="n">
-        <v>765.6</v>
+        <v>771.8</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>603</v>
+        <v>676</v>
       </c>
       <c r="C34" t="n">
-        <v>630</v>
+        <v>690</v>
       </c>
       <c r="D34" t="n">
-        <v>641</v>
+        <v>719</v>
       </c>
       <c r="E34" t="n">
-        <v>721</v>
+        <v>650</v>
       </c>
       <c r="F34" t="n">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="G34" t="n">
-        <v>621</v>
+        <v>648</v>
       </c>
       <c r="H34" t="n">
-        <v>650</v>
+        <v>704</v>
       </c>
       <c r="I34" t="n">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="J34" t="n">
-        <v>656</v>
+        <v>706</v>
       </c>
       <c r="K34" t="n">
-        <v>645</v>
+        <v>746</v>
       </c>
       <c r="L34" t="n">
-        <v>660.3</v>
+        <v>695.9</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>766</v>
+        <v>707</v>
       </c>
       <c r="C35" t="n">
-        <v>768</v>
+        <v>719</v>
       </c>
       <c r="D35" t="n">
-        <v>767</v>
+        <v>806</v>
       </c>
       <c r="E35" t="n">
-        <v>780</v>
+        <v>731</v>
       </c>
       <c r="F35" t="n">
-        <v>736</v>
+        <v>776</v>
       </c>
       <c r="G35" t="n">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="H35" t="n">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="I35" t="n">
-        <v>833</v>
+        <v>704</v>
       </c>
       <c r="J35" t="n">
-        <v>739</v>
+        <v>807</v>
       </c>
       <c r="K35" t="n">
-        <v>776</v>
+        <v>816</v>
       </c>
       <c r="L35" t="n">
-        <v>772.4</v>
+        <v>761.2</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>601</v>
+        <v>565</v>
       </c>
       <c r="C36" t="n">
-        <v>708</v>
+        <v>641</v>
       </c>
       <c r="D36" t="n">
-        <v>626</v>
+        <v>546</v>
       </c>
       <c r="E36" t="n">
-        <v>674</v>
+        <v>591</v>
       </c>
       <c r="F36" t="n">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="G36" t="n">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="H36" t="n">
-        <v>648</v>
+        <v>549</v>
       </c>
       <c r="I36" t="n">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="J36" t="n">
-        <v>539</v>
+        <v>595</v>
       </c>
       <c r="K36" t="n">
-        <v>622</v>
+        <v>706</v>
       </c>
       <c r="L36" t="n">
-        <v>621.7</v>
+        <v>599.8</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>709</v>
+        <v>676</v>
       </c>
       <c r="C37" t="n">
+        <v>711</v>
+      </c>
+      <c r="D37" t="n">
+        <v>728</v>
+      </c>
+      <c r="E37" t="n">
+        <v>826</v>
+      </c>
+      <c r="F37" t="n">
+        <v>678</v>
+      </c>
+      <c r="G37" t="n">
+        <v>660</v>
+      </c>
+      <c r="H37" t="n">
+        <v>704</v>
+      </c>
+      <c r="I37" t="n">
+        <v>727</v>
+      </c>
+      <c r="J37" t="n">
+        <v>734</v>
+      </c>
+      <c r="K37" t="n">
         <v>714</v>
       </c>
-      <c r="D37" t="n">
-        <v>638</v>
-      </c>
-      <c r="E37" t="n">
-        <v>639</v>
-      </c>
-      <c r="F37" t="n">
-        <v>729</v>
-      </c>
-      <c r="G37" t="n">
-        <v>676</v>
-      </c>
-      <c r="H37" t="n">
-        <v>709</v>
-      </c>
-      <c r="I37" t="n">
-        <v>740</v>
-      </c>
-      <c r="J37" t="n">
-        <v>721</v>
-      </c>
-      <c r="K37" t="n">
-        <v>690</v>
-      </c>
       <c r="L37" t="n">
-        <v>696.5</v>
+        <v>715.8</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
+        <v>740</v>
+      </c>
+      <c r="C38" t="n">
+        <v>688</v>
+      </c>
+      <c r="D38" t="n">
+        <v>698</v>
+      </c>
+      <c r="E38" t="n">
+        <v>731</v>
+      </c>
+      <c r="F38" t="n">
         <v>703</v>
       </c>
-      <c r="C38" t="n">
-        <v>708</v>
-      </c>
-      <c r="D38" t="n">
-        <v>856</v>
-      </c>
-      <c r="E38" t="n">
-        <v>734</v>
-      </c>
-      <c r="F38" t="n">
-        <v>824</v>
-      </c>
       <c r="G38" t="n">
-        <v>783</v>
+        <v>721</v>
       </c>
       <c r="H38" t="n">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="I38" t="n">
-        <v>828</v>
+        <v>774</v>
       </c>
       <c r="J38" t="n">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="K38" t="n">
-        <v>720</v>
+        <v>737</v>
       </c>
       <c r="L38" t="n">
-        <v>756.1</v>
+        <v>720.3</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
+        <v>615</v>
+      </c>
+      <c r="C39" t="n">
+        <v>569</v>
+      </c>
+      <c r="D39" t="n">
+        <v>556</v>
+      </c>
+      <c r="E39" t="n">
         <v>618</v>
       </c>
-      <c r="C39" t="n">
-        <v>578</v>
-      </c>
-      <c r="D39" t="n">
-        <v>633</v>
-      </c>
-      <c r="E39" t="n">
-        <v>566</v>
-      </c>
       <c r="F39" t="n">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="G39" t="n">
-        <v>582</v>
+        <v>661</v>
       </c>
       <c r="H39" t="n">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="I39" t="n">
-        <v>520</v>
+        <v>584</v>
       </c>
       <c r="J39" t="n">
-        <v>614</v>
+        <v>705</v>
       </c>
       <c r="K39" t="n">
-        <v>561</v>
+        <v>647</v>
       </c>
       <c r="L39" t="n">
-        <v>581.2</v>
+        <v>608.1</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="C40" t="n">
-        <v>790</v>
+        <v>868</v>
       </c>
       <c r="D40" t="n">
-        <v>878</v>
+        <v>772</v>
       </c>
       <c r="E40" t="n">
-        <v>705</v>
+        <v>823</v>
       </c>
       <c r="F40" t="n">
+        <v>731</v>
+      </c>
+      <c r="G40" t="n">
+        <v>780</v>
+      </c>
+      <c r="H40" t="n">
+        <v>732</v>
+      </c>
+      <c r="I40" t="n">
+        <v>756</v>
+      </c>
+      <c r="J40" t="n">
+        <v>837</v>
+      </c>
+      <c r="K40" t="n">
         <v>729</v>
       </c>
-      <c r="G40" t="n">
-        <v>754</v>
-      </c>
-      <c r="H40" t="n">
-        <v>694</v>
-      </c>
-      <c r="I40" t="n">
-        <v>792</v>
-      </c>
-      <c r="J40" t="n">
-        <v>752</v>
-      </c>
-      <c r="K40" t="n">
-        <v>754</v>
-      </c>
       <c r="L40" t="n">
-        <v>766.9</v>
+        <v>787.9</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>737</v>
+        <v>653</v>
       </c>
       <c r="C41" t="n">
-        <v>625</v>
+        <v>589</v>
       </c>
       <c r="D41" t="n">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="E41" t="n">
-        <v>648</v>
+        <v>674</v>
       </c>
       <c r="F41" t="n">
-        <v>714</v>
+        <v>617</v>
       </c>
       <c r="G41" t="n">
-        <v>597</v>
+        <v>661</v>
       </c>
       <c r="H41" t="n">
-        <v>721</v>
+        <v>636</v>
       </c>
       <c r="I41" t="n">
-        <v>666</v>
+        <v>698</v>
       </c>
       <c r="J41" t="n">
-        <v>645</v>
+        <v>622</v>
       </c>
       <c r="K41" t="n">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="L41" t="n">
-        <v>667.8</v>
+        <v>644.1</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>662</v>
+        <v>686</v>
       </c>
       <c r="C42" t="n">
-        <v>608</v>
+        <v>635</v>
       </c>
       <c r="D42" t="n">
-        <v>739</v>
+        <v>632</v>
       </c>
       <c r="E42" t="n">
-        <v>706</v>
+        <v>611</v>
       </c>
       <c r="F42" t="n">
-        <v>641</v>
+        <v>698</v>
       </c>
       <c r="G42" t="n">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="H42" t="n">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="I42" t="n">
-        <v>623</v>
+        <v>704</v>
       </c>
       <c r="J42" t="n">
-        <v>679</v>
+        <v>771</v>
       </c>
       <c r="K42" t="n">
-        <v>667</v>
+        <v>613</v>
       </c>
       <c r="L42" t="n">
-        <v>664.8</v>
+        <v>671</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>743</v>
+        <v>695</v>
       </c>
       <c r="C43" t="n">
-        <v>792</v>
+        <v>693</v>
       </c>
       <c r="D43" t="n">
-        <v>728</v>
+        <v>814</v>
       </c>
       <c r="E43" t="n">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="F43" t="n">
-        <v>747</v>
+        <v>970</v>
       </c>
       <c r="G43" t="n">
-        <v>801</v>
+        <v>832</v>
       </c>
       <c r="H43" t="n">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="I43" t="n">
-        <v>809</v>
+        <v>680</v>
       </c>
       <c r="J43" t="n">
-        <v>683</v>
+        <v>707</v>
       </c>
       <c r="K43" t="n">
-        <v>832</v>
+        <v>776</v>
       </c>
       <c r="L43" t="n">
-        <v>762.7</v>
+        <v>765.6</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>828</v>
+        <v>754</v>
       </c>
       <c r="C44" t="n">
-        <v>848</v>
+        <v>767</v>
       </c>
       <c r="D44" t="n">
-        <v>793</v>
+        <v>757</v>
       </c>
       <c r="E44" t="n">
-        <v>830</v>
+        <v>724</v>
       </c>
       <c r="F44" t="n">
-        <v>764</v>
+        <v>708</v>
       </c>
       <c r="G44" t="n">
-        <v>787</v>
+        <v>742</v>
       </c>
       <c r="H44" t="n">
-        <v>743</v>
+        <v>722</v>
       </c>
       <c r="I44" t="n">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="J44" t="n">
-        <v>846</v>
+        <v>727</v>
       </c>
       <c r="K44" t="n">
-        <v>704</v>
+        <v>775</v>
       </c>
       <c r="L44" t="n">
-        <v>790.8</v>
+        <v>743.8</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="C45" t="n">
-        <v>597</v>
+        <v>761</v>
       </c>
       <c r="D45" t="n">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E45" t="n">
-        <v>607</v>
+        <v>563</v>
       </c>
       <c r="F45" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G45" t="n">
-        <v>574</v>
+        <v>618</v>
       </c>
       <c r="H45" t="n">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="I45" t="n">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="J45" t="n">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="K45" t="n">
-        <v>640</v>
+        <v>588</v>
       </c>
       <c r="L45" t="n">
-        <v>596.5</v>
+        <v>609.1</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>613</v>
+        <v>640</v>
       </c>
       <c r="C46" t="n">
-        <v>881</v>
+        <v>615</v>
       </c>
       <c r="D46" t="n">
-        <v>676</v>
+        <v>712</v>
       </c>
       <c r="E46" t="n">
-        <v>728</v>
+        <v>682</v>
       </c>
       <c r="F46" t="n">
-        <v>665</v>
+        <v>781</v>
       </c>
       <c r="G46" t="n">
-        <v>648</v>
+        <v>705</v>
       </c>
       <c r="H46" t="n">
-        <v>711</v>
+        <v>680</v>
       </c>
       <c r="I46" t="n">
-        <v>623</v>
+        <v>640</v>
       </c>
       <c r="J46" t="n">
-        <v>776</v>
+        <v>717</v>
       </c>
       <c r="K46" t="n">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="L46" t="n">
-        <v>699.7</v>
+        <v>686.8</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>709</v>
+        <v>759</v>
       </c>
       <c r="C47" t="n">
-        <v>669</v>
+        <v>844</v>
       </c>
       <c r="D47" t="n">
-        <v>839</v>
+        <v>802</v>
       </c>
       <c r="E47" t="n">
-        <v>840</v>
+        <v>861</v>
       </c>
       <c r="F47" t="n">
-        <v>976</v>
+        <v>719</v>
       </c>
       <c r="G47" t="n">
-        <v>713</v>
+        <v>799</v>
       </c>
       <c r="H47" t="n">
-        <v>875</v>
+        <v>726</v>
       </c>
       <c r="I47" t="n">
-        <v>848</v>
+        <v>936</v>
       </c>
       <c r="J47" t="n">
-        <v>684</v>
+        <v>816</v>
       </c>
       <c r="K47" t="n">
-        <v>903</v>
+        <v>698</v>
       </c>
       <c r="L47" t="n">
-        <v>805.6</v>
+        <v>796</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>661</v>
+        <v>610</v>
       </c>
       <c r="C48" t="n">
-        <v>629</v>
+        <v>760</v>
       </c>
       <c r="D48" t="n">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="E48" t="n">
+        <v>638</v>
+      </c>
+      <c r="F48" t="n">
+        <v>688</v>
+      </c>
+      <c r="G48" t="n">
+        <v>646</v>
+      </c>
+      <c r="H48" t="n">
+        <v>737</v>
+      </c>
+      <c r="I48" t="n">
         <v>662</v>
       </c>
-      <c r="F48" t="n">
-        <v>714</v>
-      </c>
-      <c r="G48" t="n">
-        <v>693</v>
-      </c>
-      <c r="H48" t="n">
-        <v>765</v>
-      </c>
-      <c r="I48" t="n">
-        <v>731</v>
-      </c>
       <c r="J48" t="n">
-        <v>662</v>
+        <v>633</v>
       </c>
       <c r="K48" t="n">
-        <v>770</v>
+        <v>646</v>
       </c>
       <c r="L48" t="n">
-        <v>692.7</v>
+        <v>667.2</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>805</v>
+        <v>754</v>
       </c>
       <c r="C49" t="n">
-        <v>815</v>
+        <v>828</v>
       </c>
       <c r="D49" t="n">
-        <v>803</v>
+        <v>745</v>
       </c>
       <c r="E49" t="n">
-        <v>693</v>
+        <v>844</v>
       </c>
       <c r="F49" t="n">
-        <v>820</v>
+        <v>794</v>
       </c>
       <c r="G49" t="n">
-        <v>841</v>
+        <v>824</v>
       </c>
       <c r="H49" t="n">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="I49" t="n">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="J49" t="n">
-        <v>755</v>
+        <v>867</v>
       </c>
       <c r="K49" t="n">
-        <v>790</v>
+        <v>744</v>
       </c>
       <c r="L49" t="n">
-        <v>788.3</v>
+        <v>796.5</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="C50" t="n">
-        <v>689</v>
+        <v>702</v>
       </c>
       <c r="D50" t="n">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E50" t="n">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="F50" t="n">
-        <v>645</v>
+        <v>611</v>
       </c>
       <c r="G50" t="n">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H50" t="n">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="I50" t="n">
-        <v>609</v>
+        <v>658</v>
       </c>
       <c r="J50" t="n">
-        <v>684</v>
+        <v>628</v>
       </c>
       <c r="K50" t="n">
-        <v>691</v>
+        <v>667</v>
       </c>
       <c r="L50" t="n">
-        <v>652</v>
+        <v>646.8</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>746</v>
+        <v>719</v>
       </c>
       <c r="C51" t="n">
-        <v>691</v>
+        <v>727</v>
       </c>
       <c r="D51" t="n">
-        <v>680</v>
+        <v>732</v>
       </c>
       <c r="E51" t="n">
-        <v>688</v>
+        <v>803</v>
       </c>
       <c r="F51" t="n">
-        <v>705</v>
+        <v>726</v>
       </c>
       <c r="G51" t="n">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="H51" t="n">
-        <v>652</v>
+        <v>721</v>
       </c>
       <c r="I51" t="n">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J51" t="n">
-        <v>731</v>
+        <v>781</v>
       </c>
       <c r="K51" t="n">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="L51" t="n">
-        <v>695.7</v>
+        <v>725.7</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>720.36</v>
+        <v>712.4</v>
       </c>
       <c r="C52" t="n">
-        <v>714.3200000000001</v>
+        <v>712.7</v>
       </c>
       <c r="D52" t="n">
-        <v>726.46</v>
+        <v>723.42</v>
       </c>
       <c r="E52" t="n">
-        <v>723.78</v>
+        <v>722.54</v>
       </c>
       <c r="F52" t="n">
-        <v>715.7</v>
+        <v>716.36</v>
       </c>
       <c r="G52" t="n">
-        <v>711.78</v>
+        <v>716.2</v>
       </c>
       <c r="H52" t="n">
-        <v>715.76</v>
+        <v>722.36</v>
       </c>
       <c r="I52" t="n">
-        <v>722.88</v>
+        <v>716.12</v>
       </c>
       <c r="J52" t="n">
-        <v>714.9400000000001</v>
+        <v>716.08</v>
       </c>
       <c r="K52" t="n">
-        <v>726.6</v>
+        <v>720.92</v>
       </c>
       <c r="L52" t="n">
-        <v>719.2579999999999</v>
+        <v>717.91</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6.25480055809021</v>
+        <v>5.074447154998779</v>
       </c>
       <c r="C2" t="n">
-        <v>4.453956842422485</v>
+        <v>5.0723557472229</v>
       </c>
       <c r="D2" t="n">
-        <v>4.070404529571533</v>
+        <v>4.256208419799805</v>
       </c>
       <c r="E2" t="n">
-        <v>4.792486906051636</v>
+        <v>4.848280429840088</v>
       </c>
       <c r="F2" t="n">
-        <v>4.244958639144897</v>
+        <v>4.730427742004395</v>
       </c>
       <c r="G2" t="n">
-        <v>3.980682849884033</v>
+        <v>4.267426252365112</v>
       </c>
       <c r="H2" t="n">
-        <v>4.08087158203125</v>
+        <v>4.70871114730835</v>
       </c>
       <c r="I2" t="n">
-        <v>4.615000247955322</v>
+        <v>4.398032665252686</v>
       </c>
       <c r="J2" t="n">
-        <v>4.422379732131958</v>
+        <v>4.322321891784668</v>
       </c>
       <c r="K2" t="n">
-        <v>3.825105905532837</v>
+        <v>4.981730937957764</v>
       </c>
       <c r="L2" t="n">
-        <v>4.474064779281616</v>
+        <v>4.665994238853455</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.404597997665405</v>
+        <v>4.770216464996338</v>
       </c>
       <c r="C3" t="n">
-        <v>4.298302173614502</v>
+        <v>4.669813871383667</v>
       </c>
       <c r="D3" t="n">
-        <v>4.800541877746582</v>
+        <v>4.769916296005249</v>
       </c>
       <c r="E3" t="n">
-        <v>4.564893007278442</v>
+        <v>4.458769559860229</v>
       </c>
       <c r="F3" t="n">
-        <v>4.676341772079468</v>
+        <v>5.196720838546753</v>
       </c>
       <c r="G3" t="n">
-        <v>4.709275722503662</v>
+        <v>4.592306137084961</v>
       </c>
       <c r="H3" t="n">
-        <v>4.757646799087524</v>
+        <v>4.91914963722229</v>
       </c>
       <c r="I3" t="n">
-        <v>5.035916566848755</v>
+        <v>4.639907836914062</v>
       </c>
       <c r="J3" t="n">
-        <v>5.188571691513062</v>
+        <v>4.619701385498047</v>
       </c>
       <c r="K3" t="n">
-        <v>5.964448928833008</v>
+        <v>4.395001649856567</v>
       </c>
       <c r="L3" t="n">
-        <v>4.840053653717041</v>
+        <v>4.703150367736816</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.838687896728516</v>
+        <v>5.776048898696899</v>
       </c>
       <c r="C4" t="n">
-        <v>4.753417491912842</v>
+        <v>4.910481929779053</v>
       </c>
       <c r="D4" t="n">
-        <v>5.110475301742554</v>
+        <v>4.833122491836548</v>
       </c>
       <c r="E4" t="n">
-        <v>4.759015560150146</v>
+        <v>4.741885185241699</v>
       </c>
       <c r="F4" t="n">
-        <v>5.093401908874512</v>
+        <v>5.408229351043701</v>
       </c>
       <c r="G4" t="n">
-        <v>5.236680746078491</v>
+        <v>4.873570680618286</v>
       </c>
       <c r="H4" t="n">
-        <v>4.685575246810913</v>
+        <v>4.898994207382202</v>
       </c>
       <c r="I4" t="n">
-        <v>5.725986957550049</v>
+        <v>4.658756017684937</v>
       </c>
       <c r="J4" t="n">
-        <v>5.300041913986206</v>
+        <v>4.57582426071167</v>
       </c>
       <c r="K4" t="n">
-        <v>4.868776798248291</v>
+        <v>5.043810606002808</v>
       </c>
       <c r="L4" t="n">
-        <v>5.037205982208252</v>
+        <v>4.97207236289978</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>5.865777730941772</v>
+        <v>5.5564866065979</v>
       </c>
       <c r="C5" t="n">
-        <v>5.260832786560059</v>
+        <v>4.994422435760498</v>
       </c>
       <c r="D5" t="n">
-        <v>5.692206621170044</v>
+        <v>5.315757751464844</v>
       </c>
       <c r="E5" t="n">
-        <v>5.964580297470093</v>
+        <v>5.410870313644409</v>
       </c>
       <c r="F5" t="n">
-        <v>5.816902637481689</v>
+        <v>5.214886426925659</v>
       </c>
       <c r="G5" t="n">
-        <v>5.439867258071899</v>
+        <v>5.752538442611694</v>
       </c>
       <c r="H5" t="n">
-        <v>5.68073844909668</v>
+        <v>5.694204807281494</v>
       </c>
       <c r="I5" t="n">
-        <v>5.995176553726196</v>
+        <v>5.217883348464966</v>
       </c>
       <c r="J5" t="n">
-        <v>5.582214117050171</v>
+        <v>6.019254446029663</v>
       </c>
       <c r="K5" t="n">
-        <v>5.668774366378784</v>
+        <v>5.24803900718689</v>
       </c>
       <c r="L5" t="n">
-        <v>5.696707081794739</v>
+        <v>5.442434358596802</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>4.060666799545288</v>
+        <v>4.569688558578491</v>
       </c>
       <c r="C6" t="n">
-        <v>4.22873330116272</v>
+        <v>4.191867828369141</v>
       </c>
       <c r="D6" t="n">
-        <v>3.985332250595093</v>
+        <v>4.311258316040039</v>
       </c>
       <c r="E6" t="n">
-        <v>4.360163927078247</v>
+        <v>4.273735046386719</v>
       </c>
       <c r="F6" t="n">
-        <v>3.862205505371094</v>
+        <v>3.993095636367798</v>
       </c>
       <c r="G6" t="n">
-        <v>3.814272880554199</v>
+        <v>4.431864500045776</v>
       </c>
       <c r="H6" t="n">
-        <v>3.887600660324097</v>
+        <v>4.205756664276123</v>
       </c>
       <c r="I6" t="n">
-        <v>4.514067888259888</v>
+        <v>4.078474044799805</v>
       </c>
       <c r="J6" t="n">
-        <v>3.694105863571167</v>
+        <v>3.863430738449097</v>
       </c>
       <c r="K6" t="n">
-        <v>3.885592699050903</v>
+        <v>4.361573934555054</v>
       </c>
       <c r="L6" t="n">
-        <v>4.02927417755127</v>
+        <v>4.228074526786804</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>5.251584768295288</v>
+        <v>4.592556715011597</v>
       </c>
       <c r="C7" t="n">
-        <v>6.17981743812561</v>
+        <v>5.449491262435913</v>
       </c>
       <c r="D7" t="n">
-        <v>5.159124135971069</v>
+        <v>5.226354360580444</v>
       </c>
       <c r="E7" t="n">
-        <v>4.925211906433105</v>
+        <v>5.795684814453125</v>
       </c>
       <c r="F7" t="n">
-        <v>4.981591463088989</v>
+        <v>4.804431676864624</v>
       </c>
       <c r="G7" t="n">
-        <v>5.126223564147949</v>
+        <v>5.428646087646484</v>
       </c>
       <c r="H7" t="n">
-        <v>4.753827095031738</v>
+        <v>4.802031993865967</v>
       </c>
       <c r="I7" t="n">
-        <v>4.790811777114868</v>
+        <v>5.340572118759155</v>
       </c>
       <c r="J7" t="n">
-        <v>5.265888452529907</v>
+        <v>5.042248010635376</v>
       </c>
       <c r="K7" t="n">
-        <v>4.733236074447632</v>
+        <v>4.720205545425415</v>
       </c>
       <c r="L7" t="n">
-        <v>5.116731667518616</v>
+        <v>5.12022225856781</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.419526338577271</v>
+        <v>4.180216312408447</v>
       </c>
       <c r="C8" t="n">
-        <v>3.908329010009766</v>
+        <v>4.042266130447388</v>
       </c>
       <c r="D8" t="n">
-        <v>4.193589925765991</v>
+        <v>4.456240177154541</v>
       </c>
       <c r="E8" t="n">
-        <v>4.308385133743286</v>
+        <v>4.751977443695068</v>
       </c>
       <c r="F8" t="n">
-        <v>4.228516101837158</v>
+        <v>4.243368148803711</v>
       </c>
       <c r="G8" t="n">
-        <v>4.315298318862915</v>
+        <v>4.100648641586304</v>
       </c>
       <c r="H8" t="n">
-        <v>3.98213005065918</v>
+        <v>4.147178649902344</v>
       </c>
       <c r="I8" t="n">
-        <v>3.915294885635376</v>
+        <v>4.359116792678833</v>
       </c>
       <c r="J8" t="n">
-        <v>3.973721504211426</v>
+        <v>4.157402038574219</v>
       </c>
       <c r="K8" t="n">
-        <v>4.502103805541992</v>
+        <v>4.228279829025269</v>
       </c>
       <c r="L8" t="n">
-        <v>4.174689507484436</v>
+        <v>4.266669416427613</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.842722654342651</v>
+        <v>3.832608699798584</v>
       </c>
       <c r="C9" t="n">
-        <v>3.789973974227905</v>
+        <v>3.828590393066406</v>
       </c>
       <c r="D9" t="n">
-        <v>3.873648405075073</v>
+        <v>4.116555213928223</v>
       </c>
       <c r="E9" t="n">
-        <v>3.873632669448853</v>
+        <v>4.123413801193237</v>
       </c>
       <c r="F9" t="n">
-        <v>3.824655532836914</v>
+        <v>3.76746392250061</v>
       </c>
       <c r="G9" t="n">
-        <v>4.009580850601196</v>
+        <v>4.113397598266602</v>
       </c>
       <c r="H9" t="n">
-        <v>3.942239999771118</v>
+        <v>3.776694297790527</v>
       </c>
       <c r="I9" t="n">
-        <v>3.764215230941772</v>
+        <v>4.049972295761108</v>
       </c>
       <c r="J9" t="n">
-        <v>3.847985506057739</v>
+        <v>4.162707567214966</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65598726272583</v>
+        <v>3.76026177406311</v>
       </c>
       <c r="L9" t="n">
-        <v>3.842464208602905</v>
+        <v>3.953166556358338</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4.861353158950806</v>
+        <v>5.201518535614014</v>
       </c>
       <c r="C10" t="n">
-        <v>4.797523736953735</v>
+        <v>5.858402252197266</v>
       </c>
       <c r="D10" t="n">
-        <v>5.577507495880127</v>
+        <v>5.018619298934937</v>
       </c>
       <c r="E10" t="n">
-        <v>4.815488338470459</v>
+        <v>5.025411367416382</v>
       </c>
       <c r="F10" t="n">
-        <v>5.692133665084839</v>
+        <v>6.316492557525635</v>
       </c>
       <c r="G10" t="n">
-        <v>5.03232479095459</v>
+        <v>5.404979705810547</v>
       </c>
       <c r="H10" t="n">
-        <v>4.890645980834961</v>
+        <v>5.031598329544067</v>
       </c>
       <c r="I10" t="n">
-        <v>5.514203548431396</v>
+        <v>6.044139385223389</v>
       </c>
       <c r="J10" t="n">
-        <v>4.976874351501465</v>
+        <v>6.064345836639404</v>
       </c>
       <c r="K10" t="n">
-        <v>5.644173860549927</v>
+        <v>5.69645094871521</v>
       </c>
       <c r="L10" t="n">
-        <v>5.180222892761231</v>
+        <v>5.566195821762085</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.756399393081665</v>
+        <v>4.512406826019287</v>
       </c>
       <c r="C11" t="n">
-        <v>4.764861822128296</v>
+        <v>4.738242149353027</v>
       </c>
       <c r="D11" t="n">
-        <v>4.623207807540894</v>
+        <v>4.417183637619019</v>
       </c>
       <c r="E11" t="n">
-        <v>4.691025972366333</v>
+        <v>4.925097465515137</v>
       </c>
       <c r="F11" t="n">
-        <v>4.511738061904907</v>
+        <v>4.54883861541748</v>
       </c>
       <c r="G11" t="n">
-        <v>4.673053503036499</v>
+        <v>4.520651817321777</v>
       </c>
       <c r="H11" t="n">
-        <v>4.826463460922241</v>
+        <v>4.692629098892212</v>
       </c>
       <c r="I11" t="n">
-        <v>4.987029790878296</v>
+        <v>4.681769132614136</v>
       </c>
       <c r="J11" t="n">
-        <v>4.67685079574585</v>
+        <v>4.472615242004395</v>
       </c>
       <c r="K11" t="n">
-        <v>4.702275276184082</v>
+        <v>4.393891572952271</v>
       </c>
       <c r="L11" t="n">
-        <v>4.721290588378906</v>
+        <v>4.590332555770874</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>4.19706916809082</v>
+        <v>4.20994758605957</v>
       </c>
       <c r="C12" t="n">
-        <v>4.371648550033569</v>
+        <v>4.324480772018433</v>
       </c>
       <c r="D12" t="n">
-        <v>4.240011930465698</v>
+        <v>4.792194604873657</v>
       </c>
       <c r="E12" t="n">
-        <v>4.336213111877441</v>
+        <v>3.859333992004395</v>
       </c>
       <c r="F12" t="n">
-        <v>4.523753881454468</v>
+        <v>4.318089008331299</v>
       </c>
       <c r="G12" t="n">
-        <v>4.395155906677246</v>
+        <v>4.195117950439453</v>
       </c>
       <c r="H12" t="n">
-        <v>4.287461519241333</v>
+        <v>4.604217290878296</v>
       </c>
       <c r="I12" t="n">
-        <v>4.624274492263794</v>
+        <v>4.030542850494385</v>
       </c>
       <c r="J12" t="n">
-        <v>4.009775161743164</v>
+        <v>4.22478985786438</v>
       </c>
       <c r="K12" t="n">
-        <v>4.708196878433228</v>
+        <v>4.018295049667358</v>
       </c>
       <c r="L12" t="n">
-        <v>4.369356060028077</v>
+        <v>4.257700896263122</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.309546947479248</v>
+        <v>4.339218139648438</v>
       </c>
       <c r="C13" t="n">
-        <v>4.159423351287842</v>
+        <v>3.946378707885742</v>
       </c>
       <c r="D13" t="n">
-        <v>4.336771965026855</v>
+        <v>4.924237489700317</v>
       </c>
       <c r="E13" t="n">
-        <v>4.280361652374268</v>
+        <v>4.015245199203491</v>
       </c>
       <c r="F13" t="n">
-        <v>3.990382194519043</v>
+        <v>4.03957986831665</v>
       </c>
       <c r="G13" t="n">
-        <v>4.42051100730896</v>
+        <v>4.563237190246582</v>
       </c>
       <c r="H13" t="n">
-        <v>4.178129911422729</v>
+        <v>4.348500967025757</v>
       </c>
       <c r="I13" t="n">
-        <v>4.116883516311646</v>
+        <v>4.698060512542725</v>
       </c>
       <c r="J13" t="n">
-        <v>4.874894857406616</v>
+        <v>4.571249723434448</v>
       </c>
       <c r="K13" t="n">
-        <v>4.035545349121094</v>
+        <v>4.529150724411011</v>
       </c>
       <c r="L13" t="n">
-        <v>4.27024507522583</v>
+        <v>4.397485852241516</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.653393745422363</v>
+        <v>4.209863662719727</v>
       </c>
       <c r="C14" t="n">
-        <v>4.872379779815674</v>
+        <v>4.498573303222656</v>
       </c>
       <c r="D14" t="n">
-        <v>4.625968217849731</v>
+        <v>4.640121698379517</v>
       </c>
       <c r="E14" t="n">
-        <v>4.221540451049805</v>
+        <v>4.728525638580322</v>
       </c>
       <c r="F14" t="n">
-        <v>4.049723625183105</v>
+        <v>4.484576225280762</v>
       </c>
       <c r="G14" t="n">
-        <v>4.114014148712158</v>
+        <v>4.445895671844482</v>
       </c>
       <c r="H14" t="n">
-        <v>4.275652170181274</v>
+        <v>4.365565776824951</v>
       </c>
       <c r="I14" t="n">
-        <v>4.325464487075806</v>
+        <v>4.321485042572021</v>
       </c>
       <c r="J14" t="n">
-        <v>3.920498609542847</v>
+        <v>4.894856452941895</v>
       </c>
       <c r="K14" t="n">
-        <v>4.211269617080688</v>
+        <v>4.179787158966064</v>
       </c>
       <c r="L14" t="n">
-        <v>4.326990485191345</v>
+        <v>4.47692506313324</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.26611328125</v>
+        <v>4.681689023971558</v>
       </c>
       <c r="C15" t="n">
-        <v>4.774938106536865</v>
+        <v>4.547577619552612</v>
       </c>
       <c r="D15" t="n">
-        <v>4.852984189987183</v>
+        <v>4.556894779205322</v>
       </c>
       <c r="E15" t="n">
-        <v>4.713231563568115</v>
+        <v>4.678704738616943</v>
       </c>
       <c r="F15" t="n">
-        <v>4.549481630325317</v>
+        <v>4.524109601974487</v>
       </c>
       <c r="G15" t="n">
-        <v>4.509747505187988</v>
+        <v>4.897215366363525</v>
       </c>
       <c r="H15" t="n">
-        <v>4.98406195640564</v>
+        <v>4.491779327392578</v>
       </c>
       <c r="I15" t="n">
-        <v>4.476364374160767</v>
+        <v>5.11269211769104</v>
       </c>
       <c r="J15" t="n">
-        <v>4.784573316574097</v>
+        <v>4.659801244735718</v>
       </c>
       <c r="K15" t="n">
-        <v>5.141159534454346</v>
+        <v>4.596790552139282</v>
       </c>
       <c r="L15" t="n">
-        <v>4.705265545845032</v>
+        <v>4.674725437164307</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.253937959671021</v>
+        <v>4.378010034561157</v>
       </c>
       <c r="C16" t="n">
-        <v>4.392587423324585</v>
+        <v>6.032143115997314</v>
       </c>
       <c r="D16" t="n">
-        <v>4.812560081481934</v>
+        <v>4.579012393951416</v>
       </c>
       <c r="E16" t="n">
-        <v>4.647915363311768</v>
+        <v>4.383408546447754</v>
       </c>
       <c r="F16" t="n">
-        <v>4.737121343612671</v>
+        <v>4.698415517807007</v>
       </c>
       <c r="G16" t="n">
-        <v>4.524230003356934</v>
+        <v>5.096943616867065</v>
       </c>
       <c r="H16" t="n">
-        <v>4.305442333221436</v>
+        <v>4.442705869674683</v>
       </c>
       <c r="I16" t="n">
-        <v>4.223244428634644</v>
+        <v>4.36274790763855</v>
       </c>
       <c r="J16" t="n">
-        <v>4.157883644104004</v>
+        <v>4.610186100006104</v>
       </c>
       <c r="K16" t="n">
-        <v>4.110064506530762</v>
+        <v>5.09971284866333</v>
       </c>
       <c r="L16" t="n">
-        <v>4.416498708724975</v>
+        <v>4.768328595161438</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.63268256187439</v>
+        <v>4.674343824386597</v>
       </c>
       <c r="C17" t="n">
-        <v>4.570069789886475</v>
+        <v>4.753471612930298</v>
       </c>
       <c r="D17" t="n">
-        <v>3.956699371337891</v>
+        <v>4.780874967575073</v>
       </c>
       <c r="E17" t="n">
-        <v>4.40450644493103</v>
+        <v>4.338557004928589</v>
       </c>
       <c r="F17" t="n">
-        <v>4.379091739654541</v>
+        <v>4.794284343719482</v>
       </c>
       <c r="G17" t="n">
-        <v>4.603037357330322</v>
+        <v>4.89462947845459</v>
       </c>
       <c r="H17" t="n">
-        <v>3.984025239944458</v>
+        <v>4.63081955909729</v>
       </c>
       <c r="I17" t="n">
-        <v>4.26113486289978</v>
+        <v>4.623077154159546</v>
       </c>
       <c r="J17" t="n">
-        <v>4.423235416412354</v>
+        <v>4.539569139480591</v>
       </c>
       <c r="K17" t="n">
-        <v>4.711495399475098</v>
+        <v>4.54626989364624</v>
       </c>
       <c r="L17" t="n">
-        <v>4.392597818374634</v>
+        <v>4.65758969783783</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>3.735971212387085</v>
+        <v>4.090485095977783</v>
       </c>
       <c r="C18" t="n">
-        <v>4.025736808776855</v>
+        <v>4.035611391067505</v>
       </c>
       <c r="D18" t="n">
-        <v>3.907536506652832</v>
+        <v>3.859657526016235</v>
       </c>
       <c r="E18" t="n">
-        <v>3.715654850006104</v>
+        <v>4.007867336273193</v>
       </c>
       <c r="F18" t="n">
-        <v>3.953954458236694</v>
+        <v>4.056957960128784</v>
       </c>
       <c r="G18" t="n">
-        <v>3.861146926879883</v>
+        <v>3.964433431625366</v>
       </c>
       <c r="H18" t="n">
-        <v>3.822261571884155</v>
+        <v>4.375605821609497</v>
       </c>
       <c r="I18" t="n">
-        <v>4.072147130966187</v>
+        <v>4.219388008117676</v>
       </c>
       <c r="J18" t="n">
-        <v>4.103044986724854</v>
+        <v>3.976078987121582</v>
       </c>
       <c r="K18" t="n">
-        <v>3.840197086334229</v>
+        <v>4.118445873260498</v>
       </c>
       <c r="L18" t="n">
-        <v>3.903765153884888</v>
+        <v>4.070453143119812</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.309529066085815</v>
+        <v>5.218831539154053</v>
       </c>
       <c r="C19" t="n">
-        <v>4.459134817123413</v>
+        <v>4.682063102722168</v>
       </c>
       <c r="D19" t="n">
-        <v>4.695898294448853</v>
+        <v>5.402116298675537</v>
       </c>
       <c r="E19" t="n">
-        <v>4.716216802597046</v>
+        <v>4.997789144515991</v>
       </c>
       <c r="F19" t="n">
-        <v>4.425469398498535</v>
+        <v>4.5815110206604</v>
       </c>
       <c r="G19" t="n">
-        <v>4.726194858551025</v>
+        <v>4.692030429840088</v>
       </c>
       <c r="H19" t="n">
-        <v>4.646882057189941</v>
+        <v>4.890955686569214</v>
       </c>
       <c r="I19" t="n">
-        <v>4.972067832946777</v>
+        <v>4.716864347457886</v>
       </c>
       <c r="J19" t="n">
-        <v>4.886759757995605</v>
+        <v>4.729970932006836</v>
       </c>
       <c r="K19" t="n">
-        <v>4.586570978164673</v>
+        <v>4.657013416290283</v>
       </c>
       <c r="L19" t="n">
-        <v>4.642472386360168</v>
+        <v>4.856914591789246</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>4.077888011932373</v>
+        <v>4.421339750289917</v>
       </c>
       <c r="C20" t="n">
-        <v>4.187095403671265</v>
+        <v>4.19166111946106</v>
       </c>
       <c r="D20" t="n">
-        <v>4.327213525772095</v>
+        <v>4.69140625</v>
       </c>
       <c r="E20" t="n">
-        <v>4.122764587402344</v>
+        <v>4.365316152572632</v>
       </c>
       <c r="F20" t="n">
-        <v>4.322256088256836</v>
+        <v>4.680014610290527</v>
       </c>
       <c r="G20" t="n">
-        <v>4.283335208892822</v>
+        <v>4.397926807403564</v>
       </c>
       <c r="H20" t="n">
-        <v>4.139732837677002</v>
+        <v>4.416565179824829</v>
       </c>
       <c r="I20" t="n">
-        <v>4.301290512084961</v>
+        <v>4.687207698822021</v>
       </c>
       <c r="J20" t="n">
-        <v>4.537190198898315</v>
+        <v>4.647455215454102</v>
       </c>
       <c r="K20" t="n">
-        <v>4.239971160888672</v>
+        <v>5.018925428390503</v>
       </c>
       <c r="L20" t="n">
-        <v>4.253873753547668</v>
+        <v>4.551781821250915</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>3.919281244277954</v>
+        <v>4.510276317596436</v>
       </c>
       <c r="C21" t="n">
-        <v>4.156201362609863</v>
+        <v>4.436524868011475</v>
       </c>
       <c r="D21" t="n">
-        <v>4.445398807525635</v>
+        <v>4.287395715713501</v>
       </c>
       <c r="E21" t="n">
-        <v>4.746173620223999</v>
+        <v>4.339200496673584</v>
       </c>
       <c r="F21" t="n">
-        <v>4.110781908035278</v>
+        <v>4.282552242279053</v>
       </c>
       <c r="G21" t="n">
-        <v>4.514735460281372</v>
+        <v>4.759487867355347</v>
       </c>
       <c r="H21" t="n">
-        <v>4.131728172302246</v>
+        <v>4.587065935134888</v>
       </c>
       <c r="I21" t="n">
-        <v>4.14022421836853</v>
+        <v>4.36028528213501</v>
       </c>
       <c r="J21" t="n">
-        <v>4.338200807571411</v>
+        <v>4.38172435760498</v>
       </c>
       <c r="K21" t="n">
-        <v>4.463879823684692</v>
+        <v>4.604763031005859</v>
       </c>
       <c r="L21" t="n">
-        <v>4.296660542488098</v>
+        <v>4.454927611351013</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.206037282943726</v>
+        <v>4.427515029907227</v>
       </c>
       <c r="C22" t="n">
-        <v>4.120429754257202</v>
+        <v>4.327290058135986</v>
       </c>
       <c r="D22" t="n">
-        <v>4.568283319473267</v>
+        <v>4.285674571990967</v>
       </c>
       <c r="E22" t="n">
-        <v>4.348910093307495</v>
+        <v>4.317550182342529</v>
       </c>
       <c r="F22" t="n">
-        <v>4.216135263442993</v>
+        <v>4.594833374023438</v>
       </c>
       <c r="G22" t="n">
-        <v>4.656168699264526</v>
+        <v>4.523773431777954</v>
       </c>
       <c r="H22" t="n">
-        <v>4.232247352600098</v>
+        <v>4.515658378601074</v>
       </c>
       <c r="I22" t="n">
-        <v>4.450150966644287</v>
+        <v>4.456443309783936</v>
       </c>
       <c r="J22" t="n">
-        <v>4.431723833084106</v>
+        <v>4.693482160568237</v>
       </c>
       <c r="K22" t="n">
-        <v>4.142942190170288</v>
+        <v>4.497963190078735</v>
       </c>
       <c r="L22" t="n">
-        <v>4.337302875518799</v>
+        <v>4.464018368721009</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.154910087585449</v>
+        <v>4.771755933761597</v>
       </c>
       <c r="C23" t="n">
-        <v>4.046445369720459</v>
+        <v>4.59151029586792</v>
       </c>
       <c r="D23" t="n">
-        <v>4.778379678726196</v>
+        <v>4.799027919769287</v>
       </c>
       <c r="E23" t="n">
-        <v>5.674086332321167</v>
+        <v>4.551994323730469</v>
       </c>
       <c r="F23" t="n">
-        <v>4.58080530166626</v>
+        <v>4.601975917816162</v>
       </c>
       <c r="G23" t="n">
-        <v>4.253671407699585</v>
+        <v>4.726598978042603</v>
       </c>
       <c r="H23" t="n">
-        <v>4.560859441757202</v>
+        <v>4.358967304229736</v>
       </c>
       <c r="I23" t="n">
-        <v>4.283563375473022</v>
+        <v>4.865947961807251</v>
       </c>
       <c r="J23" t="n">
-        <v>4.393935203552246</v>
+        <v>4.241049766540527</v>
       </c>
       <c r="K23" t="n">
-        <v>5.092981815338135</v>
+        <v>4.777637720108032</v>
       </c>
       <c r="L23" t="n">
-        <v>4.581963801383973</v>
+        <v>4.628646612167358</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.455638647079468</v>
+        <v>4.239913940429688</v>
       </c>
       <c r="C24" t="n">
-        <v>4.132962703704834</v>
+        <v>4.379305601119995</v>
       </c>
       <c r="D24" t="n">
-        <v>4.524150371551514</v>
+        <v>4.902297496795654</v>
       </c>
       <c r="E24" t="n">
-        <v>4.568603515625</v>
+        <v>4.471303462982178</v>
       </c>
       <c r="F24" t="n">
-        <v>4.223006963729858</v>
+        <v>4.096405267715454</v>
       </c>
       <c r="G24" t="n">
-        <v>4.691088438034058</v>
+        <v>4.419214248657227</v>
       </c>
       <c r="H24" t="n">
-        <v>4.360653162002563</v>
+        <v>4.147234916687012</v>
       </c>
       <c r="I24" t="n">
-        <v>4.672883987426758</v>
+        <v>5.170331954956055</v>
       </c>
       <c r="J24" t="n">
-        <v>4.815515995025635</v>
+        <v>4.181108236312866</v>
       </c>
       <c r="K24" t="n">
-        <v>4.234509706497192</v>
+        <v>4.186285495758057</v>
       </c>
       <c r="L24" t="n">
-        <v>4.467901349067688</v>
+        <v>4.419340062141418</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.151714324951172</v>
+        <v>4.002758979797363</v>
       </c>
       <c r="C25" t="n">
-        <v>4.326242208480835</v>
+        <v>3.967598915100098</v>
       </c>
       <c r="D25" t="n">
-        <v>4.014566898345947</v>
+        <v>3.893699645996094</v>
       </c>
       <c r="E25" t="n">
-        <v>3.988665580749512</v>
+        <v>3.966021299362183</v>
       </c>
       <c r="F25" t="n">
-        <v>4.145984411239624</v>
+        <v>4.097008943557739</v>
       </c>
       <c r="G25" t="n">
-        <v>4.303557157516479</v>
+        <v>4.355627775192261</v>
       </c>
       <c r="H25" t="n">
-        <v>4.137459278106689</v>
+        <v>3.791744947433472</v>
       </c>
       <c r="I25" t="n">
-        <v>4.112067937850952</v>
+        <v>4.094062566757202</v>
       </c>
       <c r="J25" t="n">
-        <v>4.038695812225342</v>
+        <v>3.896007776260376</v>
       </c>
       <c r="K25" t="n">
-        <v>4.415758371353149</v>
+        <v>3.826892614364624</v>
       </c>
       <c r="L25" t="n">
-        <v>4.16347119808197</v>
+        <v>3.989142346382141</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.970372200012207</v>
+        <v>4.970779418945312</v>
       </c>
       <c r="C26" t="n">
-        <v>4.972541809082031</v>
+        <v>4.639047622680664</v>
       </c>
       <c r="D26" t="n">
-        <v>5.480769395828247</v>
+        <v>4.852962255477905</v>
       </c>
       <c r="E26" t="n">
-        <v>4.317847967147827</v>
+        <v>4.588903665542603</v>
       </c>
       <c r="F26" t="n">
-        <v>5.155546903610229</v>
+        <v>4.756922006607056</v>
       </c>
       <c r="G26" t="n">
-        <v>4.862634181976318</v>
+        <v>4.6999671459198</v>
       </c>
       <c r="H26" t="n">
-        <v>4.711505889892578</v>
+        <v>4.58065938949585</v>
       </c>
       <c r="I26" t="n">
-        <v>4.818805456161499</v>
+        <v>4.93299388885498</v>
       </c>
       <c r="J26" t="n">
-        <v>4.906653881072998</v>
+        <v>4.629672288894653</v>
       </c>
       <c r="K26" t="n">
-        <v>4.376896381378174</v>
+        <v>5.091986179351807</v>
       </c>
       <c r="L26" t="n">
-        <v>4.857357406616211</v>
+        <v>4.774389386177063</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>4.973378896713257</v>
+        <v>4.764790058135986</v>
       </c>
       <c r="C27" t="n">
-        <v>5.457153081893921</v>
+        <v>4.944066047668457</v>
       </c>
       <c r="D27" t="n">
-        <v>4.908971071243286</v>
+        <v>4.784229040145874</v>
       </c>
       <c r="E27" t="n">
-        <v>5.011336326599121</v>
+        <v>5.139374017715454</v>
       </c>
       <c r="F27" t="n">
-        <v>4.416759014129639</v>
+        <v>5.203146696090698</v>
       </c>
       <c r="G27" t="n">
-        <v>5.346553087234497</v>
+        <v>5.227476596832275</v>
       </c>
       <c r="H27" t="n">
-        <v>4.881087064743042</v>
+        <v>5.58483099937439</v>
       </c>
       <c r="I27" t="n">
-        <v>5.204741716384888</v>
+        <v>5.271465063095093</v>
       </c>
       <c r="J27" t="n">
-        <v>4.984739303588867</v>
+        <v>4.642625331878662</v>
       </c>
       <c r="K27" t="n">
-        <v>4.943888664245605</v>
+        <v>5.236746311187744</v>
       </c>
       <c r="L27" t="n">
-        <v>5.012860822677612</v>
+        <v>5.079875016212464</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.201289892196655</v>
+        <v>4.588979244232178</v>
       </c>
       <c r="C28" t="n">
-        <v>4.494079828262329</v>
+        <v>4.629745960235596</v>
       </c>
       <c r="D28" t="n">
-        <v>4.296562910079956</v>
+        <v>4.35097336769104</v>
       </c>
       <c r="E28" t="n">
-        <v>4.111631155014038</v>
+        <v>4.318708658218384</v>
       </c>
       <c r="F28" t="n">
-        <v>4.72423529624939</v>
+        <v>4.484315633773804</v>
       </c>
       <c r="G28" t="n">
-        <v>4.549654483795166</v>
+        <v>4.246818542480469</v>
       </c>
       <c r="H28" t="n">
-        <v>4.858875036239624</v>
+        <v>4.724625825881958</v>
       </c>
       <c r="I28" t="n">
-        <v>4.370129823684692</v>
+        <v>4.486393690109253</v>
       </c>
       <c r="J28" t="n">
-        <v>4.2225182056427</v>
+        <v>4.477887868881226</v>
       </c>
       <c r="K28" t="n">
-        <v>4.34620475769043</v>
+        <v>4.491569042205811</v>
       </c>
       <c r="L28" t="n">
-        <v>4.417518138885498</v>
+        <v>4.480001783370971</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.415507555007935</v>
+        <v>4.259529829025269</v>
       </c>
       <c r="C29" t="n">
-        <v>4.52773642539978</v>
+        <v>4.471508741378784</v>
       </c>
       <c r="D29" t="n">
-        <v>5.315815687179565</v>
+        <v>4.326679229736328</v>
       </c>
       <c r="E29" t="n">
-        <v>5.006269931793213</v>
+        <v>4.837408065795898</v>
       </c>
       <c r="F29" t="n">
-        <v>4.682570934295654</v>
+        <v>4.852740049362183</v>
       </c>
       <c r="G29" t="n">
-        <v>4.556892871856689</v>
+        <v>4.389346599578857</v>
       </c>
       <c r="H29" t="n">
-        <v>4.776907205581665</v>
+        <v>4.845857620239258</v>
       </c>
       <c r="I29" t="n">
-        <v>4.569858312606812</v>
+        <v>4.358492374420166</v>
       </c>
       <c r="J29" t="n">
-        <v>4.704537868499756</v>
+        <v>4.920462131500244</v>
       </c>
       <c r="K29" t="n">
-        <v>4.296562433242798</v>
+        <v>4.74821400642395</v>
       </c>
       <c r="L29" t="n">
-        <v>4.685265922546387</v>
+        <v>4.601023864746094</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>5.16396689414978</v>
+        <v>4.479403495788574</v>
       </c>
       <c r="C30" t="n">
-        <v>4.269124507904053</v>
+        <v>4.400086402893066</v>
       </c>
       <c r="D30" t="n">
-        <v>4.127497434616089</v>
+        <v>4.34936261177063</v>
       </c>
       <c r="E30" t="n">
-        <v>4.260170698165894</v>
+        <v>4.345282793045044</v>
       </c>
       <c r="F30" t="n">
-        <v>4.515077590942383</v>
+        <v>4.201462268829346</v>
       </c>
       <c r="G30" t="n">
-        <v>4.409788608551025</v>
+        <v>4.242407321929932</v>
       </c>
       <c r="H30" t="n">
-        <v>4.041688919067383</v>
+        <v>4.391490936279297</v>
       </c>
       <c r="I30" t="n">
-        <v>4.296540975570679</v>
+        <v>4.426931619644165</v>
       </c>
       <c r="J30" t="n">
-        <v>4.802827596664429</v>
+        <v>4.356892108917236</v>
       </c>
       <c r="K30" t="n">
-        <v>4.736688375473022</v>
+        <v>4.805966377258301</v>
       </c>
       <c r="L30" t="n">
-        <v>4.462337160110474</v>
+        <v>4.399928593635559</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>3.882584095001221</v>
+        <v>4.116060256958008</v>
       </c>
       <c r="C31" t="n">
-        <v>4.159389019012451</v>
+        <v>4.21251654624939</v>
       </c>
       <c r="D31" t="n">
-        <v>3.894570112228394</v>
+        <v>3.908414840698242</v>
       </c>
       <c r="E31" t="n">
-        <v>4.129963636398315</v>
+        <v>4.065119743347168</v>
       </c>
       <c r="F31" t="n">
-        <v>3.996816635131836</v>
+        <v>4.281403303146362</v>
       </c>
       <c r="G31" t="n">
-        <v>4.065621614456177</v>
+        <v>4.282167673110962</v>
       </c>
       <c r="H31" t="n">
-        <v>4.26362133026123</v>
+        <v>4.221819639205933</v>
       </c>
       <c r="I31" t="n">
-        <v>4.137970685958862</v>
+        <v>3.979016780853271</v>
       </c>
       <c r="J31" t="n">
-        <v>4.50778603553772</v>
+        <v>4.139922142028809</v>
       </c>
       <c r="K31" t="n">
-        <v>3.948221921920776</v>
+        <v>4.366670608520508</v>
       </c>
       <c r="L31" t="n">
-        <v>4.098654508590698</v>
+        <v>4.157311153411865</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.145245313644409</v>
+        <v>4.421736240386963</v>
       </c>
       <c r="C32" t="n">
-        <v>4.150461673736572</v>
+        <v>4.549495458602905</v>
       </c>
       <c r="D32" t="n">
-        <v>4.151931285858154</v>
+        <v>4.118841886520386</v>
       </c>
       <c r="E32" t="n">
-        <v>4.922538280487061</v>
+        <v>4.774415731430054</v>
       </c>
       <c r="F32" t="n">
-        <v>4.231278657913208</v>
+        <v>4.385202884674072</v>
       </c>
       <c r="G32" t="n">
-        <v>4.509028911590576</v>
+        <v>4.307590246200562</v>
       </c>
       <c r="H32" t="n">
-        <v>5.009244918823242</v>
+        <v>4.312843561172485</v>
       </c>
       <c r="I32" t="n">
-        <v>4.311555624008179</v>
+        <v>3.99022102355957</v>
       </c>
       <c r="J32" t="n">
-        <v>4.420792579650879</v>
+        <v>4.123883724212646</v>
       </c>
       <c r="K32" t="n">
-        <v>4.477147102355957</v>
+        <v>5.169962644577026</v>
       </c>
       <c r="L32" t="n">
-        <v>4.432922434806824</v>
+        <v>4.415419340133667</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.620228290557861</v>
+        <v>4.659412860870361</v>
       </c>
       <c r="C33" t="n">
-        <v>5.235751152038574</v>
+        <v>4.429102182388306</v>
       </c>
       <c r="D33" t="n">
-        <v>4.605283260345459</v>
+        <v>4.953815698623657</v>
       </c>
       <c r="E33" t="n">
-        <v>4.746951818466187</v>
+        <v>5.045530319213867</v>
       </c>
       <c r="F33" t="n">
-        <v>4.757167339324951</v>
+        <v>4.828206539154053</v>
       </c>
       <c r="G33" t="n">
-        <v>4.39390754699707</v>
+        <v>4.664707899093628</v>
       </c>
       <c r="H33" t="n">
-        <v>4.630983114242554</v>
+        <v>5.246777534484863</v>
       </c>
       <c r="I33" t="n">
-        <v>4.706296920776367</v>
+        <v>4.671947717666626</v>
       </c>
       <c r="J33" t="n">
-        <v>4.437445402145386</v>
+        <v>4.535996913909912</v>
       </c>
       <c r="K33" t="n">
-        <v>4.44994044303894</v>
+        <v>4.6616051197052</v>
       </c>
       <c r="L33" t="n">
-        <v>4.658395528793335</v>
+        <v>4.769710278511047</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.952256679534912</v>
+        <v>4.190512418746948</v>
       </c>
       <c r="C34" t="n">
-        <v>3.722799062728882</v>
+        <v>4.140000581741333</v>
       </c>
       <c r="D34" t="n">
-        <v>3.81208324432373</v>
+        <v>4.136592388153076</v>
       </c>
       <c r="E34" t="n">
-        <v>4.128284931182861</v>
+        <v>4.084698438644409</v>
       </c>
       <c r="F34" t="n">
-        <v>3.993124723434448</v>
+        <v>4.644704103469849</v>
       </c>
       <c r="G34" t="n">
-        <v>3.939764022827148</v>
+        <v>4.051355600357056</v>
       </c>
       <c r="H34" t="n">
-        <v>4.00065541267395</v>
+        <v>4.194446086883545</v>
       </c>
       <c r="I34" t="n">
-        <v>4.591662645339966</v>
+        <v>4.001910448074341</v>
       </c>
       <c r="J34" t="n">
-        <v>3.886170387268066</v>
+        <v>4.289190292358398</v>
       </c>
       <c r="K34" t="n">
-        <v>3.711053609848022</v>
+        <v>4.252368927001953</v>
       </c>
       <c r="L34" t="n">
-        <v>3.973785471916199</v>
+        <v>4.198577928543091</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.692525625228882</v>
+        <v>4.830161809921265</v>
       </c>
       <c r="C35" t="n">
-        <v>4.987285137176514</v>
+        <v>4.849732637405396</v>
       </c>
       <c r="D35" t="n">
-        <v>4.677495718002319</v>
+        <v>5.266799688339233</v>
       </c>
       <c r="E35" t="n">
-        <v>4.954890012741089</v>
+        <v>4.749090909957886</v>
       </c>
       <c r="F35" t="n">
-        <v>4.69353723526001</v>
+        <v>4.954911708831787</v>
       </c>
       <c r="G35" t="n">
-        <v>5.070332050323486</v>
+        <v>4.858343601226807</v>
       </c>
       <c r="H35" t="n">
-        <v>5.347421169281006</v>
+        <v>5.456031799316406</v>
       </c>
       <c r="I35" t="n">
-        <v>5.190786123275757</v>
+        <v>4.871454477310181</v>
       </c>
       <c r="J35" t="n">
-        <v>4.950517416000366</v>
+        <v>5.011722564697266</v>
       </c>
       <c r="K35" t="n">
-        <v>5.073559045791626</v>
+        <v>5.281800746917725</v>
       </c>
       <c r="L35" t="n">
-        <v>4.963834953308106</v>
+        <v>5.013004994392395</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.516955852508545</v>
+        <v>3.670440673828125</v>
       </c>
       <c r="C36" t="n">
-        <v>3.541288137435913</v>
+        <v>3.771326780319214</v>
       </c>
       <c r="D36" t="n">
-        <v>3.565814733505249</v>
+        <v>3.489466905593872</v>
       </c>
       <c r="E36" t="n">
-        <v>3.507545709609985</v>
+        <v>3.551929235458374</v>
       </c>
       <c r="F36" t="n">
-        <v>3.422263860702515</v>
+        <v>3.608918428421021</v>
       </c>
       <c r="G36" t="n">
-        <v>3.700085878372192</v>
+        <v>3.518754482269287</v>
       </c>
       <c r="H36" t="n">
-        <v>3.759914875030518</v>
+        <v>3.419456720352173</v>
       </c>
       <c r="I36" t="n">
-        <v>3.64823579788208</v>
+        <v>3.462469816207886</v>
       </c>
       <c r="J36" t="n">
-        <v>3.786874771118164</v>
+        <v>3.70379376411438</v>
       </c>
       <c r="K36" t="n">
-        <v>3.460767507553101</v>
+        <v>3.826434135437012</v>
       </c>
       <c r="L36" t="n">
-        <v>3.590974712371826</v>
+        <v>3.602299094200134</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.55248236656189</v>
+        <v>4.440435409545898</v>
       </c>
       <c r="C37" t="n">
-        <v>4.714544296264648</v>
+        <v>4.438807249069214</v>
       </c>
       <c r="D37" t="n">
-        <v>4.395533084869385</v>
+        <v>4.563084602355957</v>
       </c>
       <c r="E37" t="n">
-        <v>4.608034133911133</v>
+        <v>4.959963083267212</v>
       </c>
       <c r="F37" t="n">
-        <v>4.540740251541138</v>
+        <v>4.228924751281738</v>
       </c>
       <c r="G37" t="n">
-        <v>4.563157320022583</v>
+        <v>4.6473388671875</v>
       </c>
       <c r="H37" t="n">
-        <v>4.279421091079712</v>
+        <v>4.624946355819702</v>
       </c>
       <c r="I37" t="n">
-        <v>4.576588153839111</v>
+        <v>4.481452941894531</v>
       </c>
       <c r="J37" t="n">
-        <v>4.32625937461853</v>
+        <v>4.420137166976929</v>
       </c>
       <c r="K37" t="n">
-        <v>4.363020420074463</v>
+        <v>4.547006368637085</v>
       </c>
       <c r="L37" t="n">
-        <v>4.491978049278259</v>
+        <v>4.535209679603577</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.932950496673584</v>
+        <v>4.614335060119629</v>
       </c>
       <c r="C38" t="n">
-        <v>4.604585886001587</v>
+        <v>4.716898918151855</v>
       </c>
       <c r="D38" t="n">
-        <v>4.901792764663696</v>
+        <v>4.64953875541687</v>
       </c>
       <c r="E38" t="n">
-        <v>4.831419229507446</v>
+        <v>4.778619527816772</v>
       </c>
       <c r="F38" t="n">
-        <v>4.719773530960083</v>
+        <v>4.669267177581787</v>
       </c>
       <c r="G38" t="n">
-        <v>5.184033632278442</v>
+        <v>4.569841861724854</v>
       </c>
       <c r="H38" t="n">
-        <v>5.041410207748413</v>
+        <v>4.869589567184448</v>
       </c>
       <c r="I38" t="n">
-        <v>5.568025588989258</v>
+        <v>4.924792528152466</v>
       </c>
       <c r="J38" t="n">
-        <v>4.483852386474609</v>
+        <v>4.891453504562378</v>
       </c>
       <c r="K38" t="n">
-        <v>4.433481693267822</v>
+        <v>4.516639947891235</v>
       </c>
       <c r="L38" t="n">
-        <v>4.870132541656494</v>
+        <v>4.72009768486023</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.223065614700317</v>
+        <v>3.879872798919678</v>
       </c>
       <c r="C39" t="n">
-        <v>3.800292491912842</v>
+        <v>4.037568092346191</v>
       </c>
       <c r="D39" t="n">
-        <v>4.15942645072937</v>
+        <v>4.016939401626587</v>
       </c>
       <c r="E39" t="n">
-        <v>4.332481145858765</v>
+        <v>4.17074728012085</v>
       </c>
       <c r="F39" t="n">
-        <v>3.932479619979858</v>
+        <v>3.744858741760254</v>
       </c>
       <c r="G39" t="n">
-        <v>4.238747358322144</v>
+        <v>3.963628053665161</v>
       </c>
       <c r="H39" t="n">
-        <v>4.173865556716919</v>
+        <v>4.297735929489136</v>
       </c>
       <c r="I39" t="n">
-        <v>3.91253662109375</v>
+        <v>4.021016359329224</v>
       </c>
       <c r="J39" t="n">
-        <v>4.111028909683228</v>
+        <v>4.235963821411133</v>
       </c>
       <c r="K39" t="n">
-        <v>4.15045690536499</v>
+        <v>3.983937501907349</v>
       </c>
       <c r="L39" t="n">
-        <v>4.103438067436218</v>
+        <v>4.035226798057556</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.920014142990112</v>
+        <v>4.77338171005249</v>
       </c>
       <c r="C40" t="n">
-        <v>5.085626602172852</v>
+        <v>4.865524053573608</v>
       </c>
       <c r="D40" t="n">
-        <v>5.019231557846069</v>
+        <v>5.493944883346558</v>
       </c>
       <c r="E40" t="n">
-        <v>4.448657989501953</v>
+        <v>4.690553665161133</v>
       </c>
       <c r="F40" t="n">
-        <v>4.753953695297241</v>
+        <v>4.418493509292603</v>
       </c>
       <c r="G40" t="n">
-        <v>4.566856861114502</v>
+        <v>4.703997611999512</v>
       </c>
       <c r="H40" t="n">
-        <v>4.711480379104614</v>
+        <v>4.439970254898071</v>
       </c>
       <c r="I40" t="n">
-        <v>4.605260848999023</v>
+        <v>4.823533773422241</v>
       </c>
       <c r="J40" t="n">
-        <v>4.631246328353882</v>
+        <v>4.957535743713379</v>
       </c>
       <c r="K40" t="n">
-        <v>5.031229019165039</v>
+        <v>4.587651491165161</v>
       </c>
       <c r="L40" t="n">
-        <v>4.777355742454529</v>
+        <v>4.775458669662475</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.964920043945312</v>
+        <v>4.465388059616089</v>
       </c>
       <c r="C41" t="n">
-        <v>4.529004096984863</v>
+        <v>4.271331787109375</v>
       </c>
       <c r="D41" t="n">
-        <v>5.515294313430786</v>
+        <v>4.278609752655029</v>
       </c>
       <c r="E41" t="n">
-        <v>4.953492164611816</v>
+        <v>4.43060302734375</v>
       </c>
       <c r="F41" t="n">
-        <v>4.279259204864502</v>
+        <v>4.316894769668579</v>
       </c>
       <c r="G41" t="n">
-        <v>4.53847599029541</v>
+        <v>4.320443391799927</v>
       </c>
       <c r="H41" t="n">
-        <v>4.572893857955933</v>
+        <v>4.400028228759766</v>
       </c>
       <c r="I41" t="n">
-        <v>4.317492246627808</v>
+        <v>4.306347608566284</v>
       </c>
       <c r="J41" t="n">
-        <v>4.590732097625732</v>
+        <v>4.33634352684021</v>
       </c>
       <c r="K41" t="n">
-        <v>4.902347087860107</v>
+        <v>4.165234565734863</v>
       </c>
       <c r="L41" t="n">
-        <v>4.716391110420227</v>
+        <v>4.329122471809387</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.511744737625122</v>
+        <v>4.545639991760254</v>
       </c>
       <c r="C42" t="n">
-        <v>4.626552104949951</v>
+        <v>4.726428985595703</v>
       </c>
       <c r="D42" t="n">
-        <v>5.50654411315918</v>
+        <v>4.669440746307373</v>
       </c>
       <c r="E42" t="n">
-        <v>4.806774139404297</v>
+        <v>4.394574403762817</v>
       </c>
       <c r="F42" t="n">
-        <v>5.171885251998901</v>
+        <v>4.594163179397583</v>
       </c>
       <c r="G42" t="n">
-        <v>5.316467046737671</v>
+        <v>4.611163854598999</v>
       </c>
       <c r="H42" t="n">
-        <v>6.488183259963989</v>
+        <v>4.894029140472412</v>
       </c>
       <c r="I42" t="n">
-        <v>5.132487297058105</v>
+        <v>4.813547849655151</v>
       </c>
       <c r="J42" t="n">
-        <v>5.48736572265625</v>
+        <v>4.63170862197876</v>
       </c>
       <c r="K42" t="n">
-        <v>4.781345844268799</v>
+        <v>4.722295045852661</v>
       </c>
       <c r="L42" t="n">
-        <v>5.182934951782227</v>
+        <v>4.660299181938171</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>5.02946662902832</v>
+        <v>4.730494022369385</v>
       </c>
       <c r="C43" t="n">
-        <v>5.300702095031738</v>
+        <v>4.742890119552612</v>
       </c>
       <c r="D43" t="n">
-        <v>5.147150754928589</v>
+        <v>5.292500972747803</v>
       </c>
       <c r="E43" t="n">
-        <v>4.841402053833008</v>
+        <v>4.68979287147522</v>
       </c>
       <c r="F43" t="n">
-        <v>5.045414924621582</v>
+        <v>5.640890598297119</v>
       </c>
       <c r="G43" t="n">
-        <v>5.144736766815186</v>
+        <v>5.315783500671387</v>
       </c>
       <c r="H43" t="n">
-        <v>5.109973907470703</v>
+        <v>4.96025013923645</v>
       </c>
       <c r="I43" t="n">
-        <v>5.085213661193848</v>
+        <v>4.552367448806763</v>
       </c>
       <c r="J43" t="n">
-        <v>4.894781351089478</v>
+        <v>4.940924167633057</v>
       </c>
       <c r="K43" t="n">
-        <v>5.188015460968018</v>
+        <v>5.412134885787964</v>
       </c>
       <c r="L43" t="n">
-        <v>5.078685760498047</v>
+        <v>5.027802872657776</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>5.234425783157349</v>
+        <v>4.382938146591187</v>
       </c>
       <c r="C44" t="n">
-        <v>4.431630373001099</v>
+        <v>4.486868858337402</v>
       </c>
       <c r="D44" t="n">
-        <v>4.275631666183472</v>
+        <v>4.264718294143677</v>
       </c>
       <c r="E44" t="n">
-        <v>4.440678596496582</v>
+        <v>4.283735990524292</v>
       </c>
       <c r="F44" t="n">
-        <v>4.768153190612793</v>
+        <v>4.288617372512817</v>
       </c>
       <c r="G44" t="n">
-        <v>3.953285455703735</v>
+        <v>4.355740785598755</v>
       </c>
       <c r="H44" t="n">
-        <v>4.218039035797119</v>
+        <v>4.132541418075562</v>
       </c>
       <c r="I44" t="n">
-        <v>4.653468608856201</v>
+        <v>4.267061471939087</v>
       </c>
       <c r="J44" t="n">
-        <v>4.708651304244995</v>
+        <v>4.400213956832886</v>
       </c>
       <c r="K44" t="n">
-        <v>4.820359945297241</v>
+        <v>4.248327493667603</v>
       </c>
       <c r="L44" t="n">
-        <v>4.550432395935059</v>
+        <v>4.311076378822326</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.250349283218384</v>
+        <v>4.17254114151001</v>
       </c>
       <c r="C45" t="n">
-        <v>4.212037801742554</v>
+        <v>4.698975563049316</v>
       </c>
       <c r="D45" t="n">
-        <v>4.206072568893433</v>
+        <v>4.016405820846558</v>
       </c>
       <c r="E45" t="n">
-        <v>4.111801385879517</v>
+        <v>4.179779291152954</v>
       </c>
       <c r="F45" t="n">
-        <v>4.162245988845825</v>
+        <v>4.165543556213379</v>
       </c>
       <c r="G45" t="n">
-        <v>4.124798774719238</v>
+        <v>4.244112014770508</v>
       </c>
       <c r="H45" t="n">
-        <v>4.455568552017212</v>
+        <v>3.997935056686401</v>
       </c>
       <c r="I45" t="n">
-        <v>4.494303464889526</v>
+        <v>4.188870191574097</v>
       </c>
       <c r="J45" t="n">
-        <v>4.182136535644531</v>
+        <v>4.136853694915771</v>
       </c>
       <c r="K45" t="n">
-        <v>4.496798753738403</v>
+        <v>4.200273036956787</v>
       </c>
       <c r="L45" t="n">
-        <v>4.269611310958862</v>
+        <v>4.200128936767578</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.448949337005615</v>
+        <v>4.208990335464478</v>
       </c>
       <c r="C46" t="n">
-        <v>4.731770753860474</v>
+        <v>4.317538738250732</v>
       </c>
       <c r="D46" t="n">
-        <v>4.379345178604126</v>
+        <v>4.411653757095337</v>
       </c>
       <c r="E46" t="n">
-        <v>4.932498216629028</v>
+        <v>4.345133304595947</v>
       </c>
       <c r="F46" t="n">
-        <v>4.344429492950439</v>
+        <v>4.946928739547729</v>
       </c>
       <c r="G46" t="n">
-        <v>4.691583633422852</v>
+        <v>4.390192270278931</v>
       </c>
       <c r="H46" t="n">
-        <v>4.710546731948853</v>
+        <v>4.180038452148438</v>
       </c>
       <c r="I46" t="n">
-        <v>4.136056900024414</v>
+        <v>4.315520763397217</v>
       </c>
       <c r="J46" t="n">
-        <v>4.687317609786987</v>
+        <v>4.227878332138062</v>
       </c>
       <c r="K46" t="n">
-        <v>4.420843601226807</v>
+        <v>4.829748868942261</v>
       </c>
       <c r="L46" t="n">
-        <v>4.54833414554596</v>
+        <v>4.417362356185913</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.560800790786743</v>
+        <v>4.456326961517334</v>
       </c>
       <c r="C47" t="n">
-        <v>6.131489753723145</v>
+        <v>5.137509107589722</v>
       </c>
       <c r="D47" t="n">
-        <v>5.023959636688232</v>
+        <v>4.375494003295898</v>
       </c>
       <c r="E47" t="n">
-        <v>5.202226877212524</v>
+        <v>5.155381679534912</v>
       </c>
       <c r="F47" t="n">
-        <v>5.545961141586304</v>
+        <v>4.31121301651001</v>
       </c>
       <c r="G47" t="n">
-        <v>5.163473844528198</v>
+        <v>5.116111516952515</v>
       </c>
       <c r="H47" t="n">
-        <v>5.526453018188477</v>
+        <v>4.732120513916016</v>
       </c>
       <c r="I47" t="n">
-        <v>5.277068138122559</v>
+        <v>4.747580051422119</v>
       </c>
       <c r="J47" t="n">
-        <v>4.442399263381958</v>
+        <v>4.594883918762207</v>
       </c>
       <c r="K47" t="n">
-        <v>5.142399072647095</v>
+        <v>4.56840443611145</v>
       </c>
       <c r="L47" t="n">
-        <v>5.201623153686524</v>
+        <v>4.719502520561218</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.540311098098755</v>
+        <v>4.429499626159668</v>
       </c>
       <c r="C48" t="n">
-        <v>4.44769549369812</v>
+        <v>5.388160467147827</v>
       </c>
       <c r="D48" t="n">
-        <v>5.392363309860229</v>
+        <v>4.735306024551392</v>
       </c>
       <c r="E48" t="n">
-        <v>4.487064123153687</v>
+        <v>4.554291725158691</v>
       </c>
       <c r="F48" t="n">
-        <v>4.961848974227905</v>
+        <v>4.283691644668579</v>
       </c>
       <c r="G48" t="n">
-        <v>4.266611576080322</v>
+        <v>4.229950428009033</v>
       </c>
       <c r="H48" t="n">
-        <v>4.55688738822937</v>
+        <v>4.708592891693115</v>
       </c>
       <c r="I48" t="n">
-        <v>4.917999982833862</v>
+        <v>4.483903408050537</v>
       </c>
       <c r="J48" t="n">
-        <v>4.819731950759888</v>
+        <v>4.364948511123657</v>
       </c>
       <c r="K48" t="n">
-        <v>5.009312152862549</v>
+        <v>4.702146768569946</v>
       </c>
       <c r="L48" t="n">
-        <v>4.739982604980469</v>
+        <v>4.588049149513244</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.994772911071777</v>
+        <v>4.865946769714355</v>
       </c>
       <c r="C49" t="n">
-        <v>5.185842037200928</v>
+        <v>4.599204063415527</v>
       </c>
       <c r="D49" t="n">
-        <v>5.141460180282593</v>
+        <v>4.520847797393799</v>
       </c>
       <c r="E49" t="n">
-        <v>4.418728828430176</v>
+        <v>5.150193214416504</v>
       </c>
       <c r="F49" t="n">
-        <v>5.568839311599731</v>
+        <v>5.000052452087402</v>
       </c>
       <c r="G49" t="n">
-        <v>4.866484642028809</v>
+        <v>4.852922201156616</v>
       </c>
       <c r="H49" t="n">
-        <v>4.702521800994873</v>
+        <v>4.377565860748291</v>
       </c>
       <c r="I49" t="n">
-        <v>4.521118402481079</v>
+        <v>4.965965032577515</v>
       </c>
       <c r="J49" t="n">
-        <v>4.734444141387939</v>
+        <v>4.842283725738525</v>
       </c>
       <c r="K49" t="n">
-        <v>4.858620166778564</v>
+        <v>4.604138374328613</v>
       </c>
       <c r="L49" t="n">
-        <v>4.899283242225647</v>
+        <v>4.777911949157715</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.678422927856445</v>
+        <v>3.677353143692017</v>
       </c>
       <c r="C50" t="n">
-        <v>3.745292663574219</v>
+        <v>4.181082725524902</v>
       </c>
       <c r="D50" t="n">
-        <v>3.85101056098938</v>
+        <v>4.105858325958252</v>
       </c>
       <c r="E50" t="n">
-        <v>3.677933931350708</v>
+        <v>3.797232866287231</v>
       </c>
       <c r="F50" t="n">
-        <v>3.692871332168579</v>
+        <v>4.033542156219482</v>
       </c>
       <c r="G50" t="n">
-        <v>3.650492668151855</v>
+        <v>3.8148353099823</v>
       </c>
       <c r="H50" t="n">
-        <v>3.839030265808105</v>
+        <v>3.561874389648438</v>
       </c>
       <c r="I50" t="n">
-        <v>3.978669404983521</v>
+        <v>3.923613548278809</v>
       </c>
       <c r="J50" t="n">
-        <v>3.819065809249878</v>
+        <v>3.891168594360352</v>
       </c>
       <c r="K50" t="n">
-        <v>3.74950909614563</v>
+        <v>3.657413721084595</v>
       </c>
       <c r="L50" t="n">
-        <v>3.768229866027832</v>
+        <v>3.864397478103638</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.90598464012146</v>
+        <v>5.175609111785889</v>
       </c>
       <c r="C51" t="n">
-        <v>4.275086402893066</v>
+        <v>4.418095588684082</v>
       </c>
       <c r="D51" t="n">
-        <v>4.935953378677368</v>
+        <v>4.637778282165527</v>
       </c>
       <c r="E51" t="n">
-        <v>4.884092092514038</v>
+        <v>5.137856960296631</v>
       </c>
       <c r="F51" t="n">
-        <v>4.900036334991455</v>
+        <v>4.542787313461304</v>
       </c>
       <c r="G51" t="n">
-        <v>4.647179841995239</v>
+        <v>4.23738169670105</v>
       </c>
       <c r="H51" t="n">
-        <v>4.703545331954956</v>
+        <v>4.438021183013916</v>
       </c>
       <c r="I51" t="n">
-        <v>4.50551962852478</v>
+        <v>4.473432302474976</v>
       </c>
       <c r="J51" t="n">
-        <v>5.030194520950317</v>
+        <v>5.146921396255493</v>
       </c>
       <c r="K51" t="n">
-        <v>6.447221994400024</v>
+        <v>4.438340425491333</v>
       </c>
       <c r="L51" t="n">
-        <v>4.923481416702271</v>
+        <v>4.66462242603302</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.523256058692932</v>
+        <v>4.520254044532776</v>
       </c>
       <c r="C52" t="n">
-        <v>4.527416133880616</v>
+        <v>4.570672755241394</v>
       </c>
       <c r="D52" t="n">
-        <v>4.597200517654419</v>
+        <v>4.553721733093262</v>
       </c>
       <c r="E52" t="n">
-        <v>4.552288861274719</v>
+        <v>4.551897268295289</v>
       </c>
       <c r="F52" t="n">
-        <v>4.522333278656006</v>
+        <v>4.549241428375244</v>
       </c>
       <c r="G52" t="n">
-        <v>4.530290064811706</v>
+        <v>4.545610823631287</v>
       </c>
       <c r="H52" t="n">
-        <v>4.53812123298645</v>
+        <v>4.528768305778503</v>
       </c>
       <c r="I52" t="n">
-        <v>4.588357172012329</v>
+        <v>4.538601250648498</v>
       </c>
       <c r="J52" t="n">
-        <v>4.544092645645142</v>
+        <v>4.527968983650208</v>
       </c>
       <c r="K52" t="n">
-        <v>4.58001817703247</v>
+        <v>4.572083916664123</v>
       </c>
       <c r="L52" t="n">
-        <v>4.550337414264678</v>
+        <v>4.545882050991058</v>
       </c>
     </row>
   </sheetData>
